--- a/data/personalia/Kantor Pusat.xlsx
+++ b/data/personalia/Kantor Pusat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047618f1b9410114/Desktop/p3ste-app/Fix/Personalia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F07BF1D1-BA1B-4EF6-9470-FD330C72BF39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{F07BF1D1-BA1B-4EF6-9470-FD330C72BF39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B34C5565-AE36-4B70-AEEA-F190BA54E396}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{7D1E271F-CDBB-40CF-816B-839C8A3F65D0}"/>
   </bookViews>
@@ -34,6 +34,20 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+  <si>
+    <t>Nama</t>
+  </si>
+  <si>
+    <t>NIPP</t>
+  </si>
+  <si>
+    <t>Posisi</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -383,9 +397,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06F9E8C1-D8B8-4C14-8321-0AD33FF06DA1}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/personalia/Kantor Pusat.xlsx
+++ b/data/personalia/Kantor Pusat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047618f1b9410114/Desktop/p3ste-app/Fix/Personalia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2EC12D97-7331-4D7E-89F2-494686D0BEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{2EC12D97-7331-4D7E-89F2-494686D0BEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A58A9A0D-49F0-4527-87B3-0AE81D1F0C8A}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -754,7 +754,7 @@
     <t>PMP.111292.65292</t>
   </si>
   <si>
-    <t>NIP</t>
+    <t>NIPP</t>
   </si>
 </sst>
 </file>
@@ -762,7 +762,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -830,10 +830,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>

--- a/data/personalia/Kantor Pusat.xlsx
+++ b/data/personalia/Kantor Pusat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047618f1b9410114/Desktop/p3ste-app/Fix/Personalia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{2EC12D97-7331-4D7E-89F2-494686D0BEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A58A9A0D-49F0-4527-87B3-0AE81D1F0C8A}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{2EC12D97-7331-4D7E-89F2-494686D0BEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3F3072D-89E6-469B-B75B-7DB181F50139}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="244">
   <si>
     <t>Wilayah</t>
   </si>
@@ -755,6 +755,9 @@
   </si>
   <si>
     <t>NIPP</t>
+  </si>
+  <si>
+    <t>TMT Pe+N1:T1</t>
   </si>
 </sst>
 </file>
@@ -813,7 +816,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -835,6 +838,9 @@
     </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2553,6 +2559,9 @@
       <c r="O29" s="6">
         <v>46916</v>
       </c>
+      <c r="P29" s="8" t="s">
+        <v>243</v>
+      </c>
       <c r="Q29" s="2" t="s">
         <v>236</v>
       </c>
@@ -4644,7 +4653,7 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="3">
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>LIST_DATA!$A$1:$A$9</xm:f>

--- a/data/personalia/Kantor Pusat.xlsx
+++ b/data/personalia/Kantor Pusat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047618f1b9410114/Desktop/p3ste-app/Fix/Personalia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{2EC12D97-7331-4D7E-89F2-494686D0BEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3F3072D-89E6-469B-B75B-7DB181F50139}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{2EC12D97-7331-4D7E-89F2-494686D0BEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F72F6586-1CD8-4189-B5C8-290A44372E12}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1960,6 +1960,9 @@
       <c r="K16" s="6">
         <v>46007</v>
       </c>
+      <c r="L16" s="6">
+        <v>46084</v>
+      </c>
       <c r="M16" s="6">
         <v>56980</v>
       </c>
@@ -3332,6 +3335,9 @@
       <c r="K45" s="6">
         <v>45962</v>
       </c>
+      <c r="L45" s="6">
+        <v>46084</v>
+      </c>
       <c r="M45" s="6">
         <v>56980</v>
       </c>
@@ -3422,6 +3428,9 @@
       </c>
       <c r="K47" s="6">
         <v>42552</v>
+      </c>
+      <c r="L47" s="6">
+        <v>46084</v>
       </c>
       <c r="M47" s="6">
         <v>56980</v>

--- a/data/personalia/Kantor Pusat.xlsx
+++ b/data/personalia/Kantor Pusat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047618f1b9410114/Desktop/p3ste-app/Fix/Personalia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{2EC12D97-7331-4D7E-89F2-494686D0BEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F72F6586-1CD8-4189-B5C8-290A44372E12}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{2EC12D97-7331-4D7E-89F2-494686D0BEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26B51865-AC19-418C-AFCA-80F90A113BF7}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="244">
   <si>
     <t>Wilayah</t>
   </si>
@@ -1957,6 +1957,9 @@
       <c r="I16" s="2">
         <v>4</v>
       </c>
+      <c r="J16" s="2" t="s">
+        <v>22</v>
+      </c>
       <c r="K16" s="6">
         <v>46007</v>
       </c>
@@ -4662,7 +4665,7 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>LIST_DATA!$A$1:$A$9</xm:f>

--- a/data/personalia/Kantor Pusat.xlsx
+++ b/data/personalia/Kantor Pusat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047618f1b9410114/Desktop/p3ste-app/Fix/Personalia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{2EC12D97-7331-4D7E-89F2-494686D0BEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26B51865-AC19-418C-AFCA-80F90A113BF7}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="8_{2EC12D97-7331-4D7E-89F2-494686D0BEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{871F8B7F-9472-42C7-85A8-168F44634CE8}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3150,9 +3150,6 @@
       <c r="K41" s="6">
         <v>40163</v>
       </c>
-      <c r="L41" s="6">
-        <v>32690</v>
-      </c>
       <c r="M41" s="6">
         <v>53175</v>
       </c>

--- a/data/personalia/Kantor Pusat.xlsx
+++ b/data/personalia/Kantor Pusat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047618f1b9410114/Desktop/p3ste-app/Fix/Personalia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{2EC12D97-7331-4D7E-89F2-494686D0BEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{871F8B7F-9472-42C7-85A8-168F44634CE8}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{2EC12D97-7331-4D7E-89F2-494686D0BEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{984B8AE2-57C5-4FD1-80A3-A3C9AAE2A22D}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3150,6 +3150,9 @@
       <c r="K41" s="6">
         <v>40163</v>
       </c>
+      <c r="L41" s="6">
+        <v>32690</v>
+      </c>
       <c r="M41" s="6">
         <v>53175</v>
       </c>

--- a/data/personalia/Kantor Pusat.xlsx
+++ b/data/personalia/Kantor Pusat.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047618f1b9410114/Desktop/p3ste-app/Fix/Personalia/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\18. STE APP\Personalia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{2EC12D97-7331-4D7E-89F2-494686D0BEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{984B8AE2-57C5-4FD1-80A3-A3C9AAE2A22D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00E4CD1B-3462-4224-A3D3-2911CEAE1755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,8 +16,20 @@
     <sheet name="Template Personalia" sheetId="1" r:id="rId1"/>
     <sheet name="LIST_DATA" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Template Personalia'!$A$1:$T$199</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -26,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="259">
   <si>
     <t>Wilayah</t>
   </si>
@@ -130,201 +142,627 @@
     <t>Pelaksana</t>
   </si>
   <si>
+    <t>Ass Manager</t>
+  </si>
+  <si>
+    <t>Assistant Manager</t>
+  </si>
+  <si>
+    <t>Kantor</t>
+  </si>
+  <si>
+    <t>NIPP</t>
+  </si>
+  <si>
+    <t>Quality Controller</t>
+  </si>
+  <si>
+    <t>Kepala UPT Resor</t>
+  </si>
+  <si>
+    <t>Kaur UPT Resor</t>
+  </si>
+  <si>
+    <t>Petugas Negative Check</t>
+  </si>
+  <si>
+    <t>Kepala UPT Workshop</t>
+  </si>
+  <si>
+    <t>Kaur UPT Workshop</t>
+  </si>
+  <si>
+    <t>WS LAA Mri</t>
+  </si>
+  <si>
+    <t>LAA 1.4 Thb</t>
+  </si>
+  <si>
+    <t>Teknisi</t>
+  </si>
+  <si>
+    <t>LAA 1.1 Rk</t>
+  </si>
+  <si>
+    <t>LAA 1.14 Nmo</t>
+  </si>
+  <si>
+    <t>LAA 1.2 Prp</t>
+  </si>
+  <si>
+    <t>LAA 1.3 Srp</t>
+  </si>
+  <si>
+    <t>LAA 1.5 Du</t>
+  </si>
+  <si>
+    <t>LAA 1.11 Psm</t>
+  </si>
+  <si>
+    <t>LAA 1.6 Jakk</t>
+  </si>
+  <si>
+    <t>LAA 1.7 Pse</t>
+  </si>
+  <si>
+    <t>LAA 1.8 Mri</t>
+  </si>
+  <si>
+    <t>LAA 1.9 Jng</t>
+  </si>
+  <si>
+    <t>LAA 1.10 Ckr</t>
+  </si>
+  <si>
+    <t>LAA 1.12 Dp</t>
+  </si>
+  <si>
+    <t>LAA 1.13 Boo</t>
+  </si>
+  <si>
+    <t>LAA 1.15 Bst</t>
+  </si>
+  <si>
+    <t>PMP Lanjutan</t>
+  </si>
+  <si>
+    <t>PMP Pelaksana</t>
+  </si>
+  <si>
+    <t>PRP Pelaksana</t>
+  </si>
+  <si>
+    <t>PRP Lanjutan</t>
+  </si>
+  <si>
+    <t>Calon Pekerja</t>
+  </si>
+  <si>
+    <t>Calon Pelaksana</t>
+  </si>
+  <si>
+    <t>Calon Teknisi</t>
+  </si>
+  <si>
+    <t>Calon Pelaksana Workshop</t>
+  </si>
+  <si>
+    <t>Calon Petugas Negative Check</t>
+  </si>
+  <si>
+    <t>Executive Vice President</t>
+  </si>
+  <si>
+    <t>Kepala UPT BYST</t>
+  </si>
+  <si>
+    <t>Pelaksana Workshop</t>
+  </si>
+  <si>
+    <t>Subunit of Field Service Power System 1</t>
+  </si>
+  <si>
+    <t>Subunit of Field Service Power System 2</t>
+  </si>
+  <si>
+    <t>Subunit of Field Service Signalling And Communication 1</t>
+  </si>
+  <si>
+    <t>Subunit of Field Service Signalling And Communication 2</t>
+  </si>
+  <si>
+    <t>Subunit of Workshop And OCC Signalling and Communication</t>
+  </si>
+  <si>
+    <t>Subunit of Workshop Power System And OCC Power</t>
+  </si>
+  <si>
+    <t>Vice President</t>
+  </si>
+  <si>
+    <t>VACANT</t>
+  </si>
+  <si>
     <t>Kantor Pusat</t>
   </si>
   <si>
     <t>ILING SUWOTO</t>
   </si>
   <si>
+    <t>EVP Signalling,Telecomunication, and Electricity (TS)</t>
+  </si>
+  <si>
     <t>PRAPTO UTOMO</t>
   </si>
   <si>
+    <t>VP Telecommunication and Electricity Maintenance (TSC)</t>
+  </si>
+  <si>
+    <t>PMP.261079.125961</t>
+  </si>
+  <si>
     <t>JAJA JAHIDIN</t>
   </si>
   <si>
+    <t>VP Signalling Maintenance (TSM)</t>
+  </si>
+  <si>
     <t>INDRA RIYADI</t>
   </si>
   <si>
+    <t>Manager Overhead Catenary and Thrid Rail Maintenance (TSCC)</t>
+  </si>
+  <si>
+    <t>PMP.041085.00869</t>
+  </si>
+  <si>
     <t>YAYANG RUSTAMAJI</t>
   </si>
   <si>
+    <t>Specialist of Overhead Catenary Maintenance (TSCC.1)</t>
+  </si>
+  <si>
+    <t>PMP.231071.67651</t>
+  </si>
+  <si>
     <t>GIGIH BUDIARTA</t>
   </si>
   <si>
+    <t>Specialist of Third Rail Maintenance (TSCC.2)</t>
+  </si>
+  <si>
     <t>MUKHLIS DWI NUGROHO</t>
   </si>
   <si>
+    <t>Pelaksana Overhead Catenary Maintenance (TSCC.1)</t>
+  </si>
+  <si>
     <t>VINA KUSUMA DEWI</t>
   </si>
   <si>
+    <t>PRP.180288.39320</t>
+  </si>
+  <si>
     <t>CECEP SULAIMAN</t>
   </si>
   <si>
+    <t>Manager Telecomunication Network Maintenance (TSCN)</t>
+  </si>
+  <si>
+    <t>PMP.280576.01283</t>
+  </si>
+  <si>
     <t>CAHYO TRI NUGROHO</t>
   </si>
   <si>
+    <t>Specialist of Transmission Network Maintenance (TSCN.1)</t>
+  </si>
+  <si>
+    <t>PRP.060284.57973</t>
+  </si>
+  <si>
     <t>S. SLAMET RIYADI</t>
   </si>
   <si>
+    <t>PLT Specialist of Transmission Network Maintenance (TSCN.2)</t>
+  </si>
+  <si>
+    <t>PRP.070474.126088</t>
+  </si>
+  <si>
     <t>ENDRAYANA ARDANNY</t>
   </si>
   <si>
+    <t>Manager Substantion and Power Supply Maintenance (TSCP)</t>
+  </si>
+  <si>
+    <t>PMP.070477.00838</t>
+  </si>
+  <si>
     <t>USUP</t>
   </si>
   <si>
+    <t>Specialist of Substation Maintenance (TSCP.1)</t>
+  </si>
+  <si>
     <t>ARYO PAMBUKO WICAKSONO</t>
   </si>
   <si>
+    <t>Specialist of Control Power Supply Maintenance (TSCP.2)</t>
+  </si>
+  <si>
+    <t>PMP.110889.40742</t>
+  </si>
+  <si>
     <t>MUHAMMAD YUDI PRATAMA</t>
   </si>
   <si>
+    <t>Pelaksana Substation and Power Supply Maintenance</t>
+  </si>
+  <si>
     <t>DEDI SURYANA</t>
   </si>
   <si>
+    <t>Manager Telecommunication System Maintenance (TSCS)</t>
+  </si>
+  <si>
     <t>MOHAMMAD MAKIN</t>
   </si>
   <si>
+    <t>Specialist of Railway Operation Telephone Maintenance (TSCS.1)</t>
+  </si>
+  <si>
+    <t>PMP.101274.125819</t>
+  </si>
+  <si>
     <t>ANGGA WIJAYA</t>
   </si>
   <si>
+    <t>Specialist of Train Dispatching Maintenance (TSCS.2)</t>
+  </si>
+  <si>
+    <t>PRP.100391.125963</t>
+  </si>
+  <si>
     <t>BAGUS SATRIA NUGRAHA</t>
   </si>
   <si>
+    <t>Pelaksana Railway Operation Telephone Maintenance (TSCS.1)</t>
+  </si>
+  <si>
+    <t>PRP.100893.38595</t>
+  </si>
+  <si>
     <t>AYU INDRASARI</t>
   </si>
   <si>
+    <t>Pelaksana Train Dispatching Maintenance (TSCS.2)</t>
+  </si>
+  <si>
+    <t>PRP.181094.38981</t>
+  </si>
+  <si>
     <t>HANAFI FADZILLAH</t>
   </si>
   <si>
     <t>AHMAD MAMAN</t>
   </si>
   <si>
-    <t>VACANT</t>
+    <t>Manager Electrical Signalling Maintenance (TSME)</t>
+  </si>
+  <si>
+    <t>PMP.200174.00894</t>
+  </si>
+  <si>
+    <t>Specialist of Indoor Electrical Signalling Maintenance (TSME.1)</t>
   </si>
   <si>
     <t>AGUNG SUDARMONO</t>
   </si>
   <si>
+    <t>Specialist of Outdoor Electrical Signalling Maintenance (TSME.2)</t>
+  </si>
+  <si>
     <t>REINANDA AVRELLITA</t>
   </si>
   <si>
+    <t>Pelaksana Indoor Electrical Signalling Maintenance</t>
+  </si>
+  <si>
     <t>ADE MAPILAYA</t>
   </si>
   <si>
+    <t>Manager Mechanical Signalling Maintenance (TSMM)</t>
+  </si>
+  <si>
+    <t>PMP.070178.00892</t>
+  </si>
+  <si>
     <t>ALDI EKO SETIANTONO</t>
   </si>
   <si>
+    <t>PLT Specialist of Indoor Mechanical Signalling Maintenance (TSMM.1)</t>
+  </si>
+  <si>
+    <t>PRP.300893.42146</t>
+  </si>
+  <si>
+    <t>PMP.300893.67108</t>
+  </si>
+  <si>
     <t>DEDI ROSADI</t>
   </si>
   <si>
+    <t>PLT Specialist of Outdoor Mechanical Signalling Maintenance (TSMM.2)</t>
+  </si>
+  <si>
+    <t>PRP.040272.57047</t>
+  </si>
+  <si>
+    <t>PMP.040272.67721</t>
+  </si>
+  <si>
     <t>REGINA NESTI APRILIA</t>
   </si>
   <si>
+    <t>Pelaksana Indoor Mechanical Signalling Maintenance</t>
+  </si>
+  <si>
     <t>MOH SOBIRIN</t>
   </si>
   <si>
+    <t>Manager Train Control Maintenance (TSMT)</t>
+  </si>
+  <si>
+    <t>PMP.051176.00857</t>
+  </si>
+  <si>
     <t>CHANDRA DWI PUTRA</t>
   </si>
   <si>
+    <t>Specialist of Onboard Equipment Maintenance (TSMT.1)</t>
+  </si>
+  <si>
     <t>LUTHFI ACHSAN</t>
   </si>
   <si>
+    <t>Specialist of Train Supervisory Maintenance (TSMT.2)</t>
+  </si>
+  <si>
     <t>AGUSTINUS DWI PRABOWO BUDI</t>
   </si>
   <si>
+    <t>Manager Wayside Equipment Maintenance (TSMW)</t>
+  </si>
+  <si>
+    <t>PMP.180577.00831</t>
+  </si>
+  <si>
     <t>DUWI DARMO</t>
   </si>
   <si>
+    <t>Specialist of Trackside ATP/ATO Maintenance (TSMW.1)</t>
+  </si>
+  <si>
+    <t>PMP.250376.75602</t>
+  </si>
+  <si>
     <t>DERMAWAN DJOKO PRIONO</t>
   </si>
   <si>
+    <t>Specialist of Trackside To Train Communication Maintenance (TSMW.2)</t>
+  </si>
+  <si>
+    <t>PRP.190977.38954</t>
+  </si>
+  <si>
     <t>FRIDA DWI OKTAVIANI</t>
   </si>
   <si>
+    <t>Pelaksana Trackside ATP/ATO Maintenance (TSMW.1)</t>
+  </si>
+  <si>
     <t>MUHAMMAD FATHKHUL HAKIM</t>
   </si>
   <si>
+    <t>Manager STE Program, Budgeting, Evaluation and Technical Support (TSSP)</t>
+  </si>
+  <si>
     <t>SUHARYONO</t>
   </si>
   <si>
+    <t>Specialist of STE Program and Administration (TSSP.1)</t>
+  </si>
+  <si>
+    <t>PMP.240573.128282</t>
+  </si>
+  <si>
     <t>NANANG TRISNADIK</t>
   </si>
   <si>
+    <t>Specialist of STE Budgeting and Procurement (TSSP.2)</t>
+  </si>
+  <si>
+    <t>PMP.080790.125984</t>
+  </si>
+  <si>
     <t>SANUSI ZULFIRMAN LUBIS</t>
   </si>
   <si>
+    <t>Specialist of STE Evaluation (TSSP.3)</t>
+  </si>
+  <si>
     <t>EDWIN ROZZAQ PRASETYO</t>
   </si>
   <si>
+    <t>Specialist of STE Technical Support (TSSP.4)</t>
+  </si>
+  <si>
+    <t>PMP.080590.125836</t>
+  </si>
+  <si>
     <t>NETALIA SOFYAN</t>
   </si>
   <si>
+    <t>Pelaksana STE Program and Administration (TSSP.1)</t>
+  </si>
+  <si>
     <t>AHMAD FADLI</t>
   </si>
   <si>
+    <t>Pelaksana STE Evaluation (TSSP.3)</t>
+  </si>
+  <si>
     <t>AMEILIA WULANDARI</t>
   </si>
   <si>
+    <t>Pelaksana STE Budgeting and Procurement (TSSP.2)</t>
+  </si>
+  <si>
     <t>AGENG MULYA</t>
   </si>
   <si>
+    <t>Kepala UPT Balai Yasa Sintelis dan LAA Kiaracondong (TSSS)</t>
+  </si>
+  <si>
     <t>YASSER YUSRAN</t>
   </si>
   <si>
+    <t>Specialist of Hardware, Software and Integration Analysis</t>
+  </si>
+  <si>
     <t>AHMAD KADAFI</t>
   </si>
   <si>
+    <t>Specialist of Tools Calibration</t>
+  </si>
+  <si>
     <t>ANDI PURWANTO</t>
   </si>
   <si>
+    <t>AM of STE Workshop Planning and Administration (TSSS.1)</t>
+  </si>
+  <si>
+    <t>PMP.020478.00952</t>
+  </si>
+  <si>
     <t>IYUS YUSEP</t>
   </si>
   <si>
+    <t>Specialist Tools and Facility</t>
+  </si>
+  <si>
     <t>FIRHANY ARDIA NUGRAHA</t>
   </si>
   <si>
+    <t>Pelaksana STE Workshop Planning and Administration (TSSS.1)</t>
+  </si>
+  <si>
+    <t>PRP.230298.64267</t>
+  </si>
+  <si>
     <t>YUDHA SUPRAYUDA</t>
   </si>
   <si>
+    <t>AM STE Workshop Engineering (TSSS.2)</t>
+  </si>
+  <si>
     <t>NOOR MUTTAQIN ARROZZY</t>
   </si>
   <si>
+    <t>Specialist of Overhead Line/ Catenary Engineering</t>
+  </si>
+  <si>
     <t>DWI LINGGA ADIPUTRA</t>
   </si>
   <si>
+    <t>Specialist of Signal Engineering</t>
+  </si>
+  <si>
+    <t>PRP.08091993.36450</t>
+  </si>
+  <si>
     <t>ANDIKA DWI PUTRA</t>
   </si>
   <si>
+    <t>Specialist of Telecommunication Engineering</t>
+  </si>
+  <si>
+    <t>PRP.191295.47000</t>
+  </si>
+  <si>
     <t>YOANITA WIDYA PUSPANINGSIH</t>
   </si>
   <si>
+    <t>Pelaksana STE Workshop Engineering (TSSS.2)</t>
+  </si>
+  <si>
+    <t>PRP.210594.39321</t>
+  </si>
+  <si>
     <t>RASYID SAIFULHAQ</t>
   </si>
   <si>
+    <t>PRP.120599.66072</t>
+  </si>
+  <si>
     <t>GANJAR PUNTO RATNOWO</t>
   </si>
   <si>
+    <t>PRP.280296.72027</t>
+  </si>
+  <si>
     <t>RAHMAT HIDAYAT</t>
   </si>
   <si>
+    <t>PRP.040797.74257</t>
+  </si>
+  <si>
     <t>FACHRY WIRAWAN PRIYANTO</t>
   </si>
   <si>
     <t>NAJIB FATONI</t>
   </si>
   <si>
+    <t>PLT AM STE Workshop Production and Repair (TSSS.3)</t>
+  </si>
+  <si>
+    <t>PRP.111292.41348</t>
+  </si>
+  <si>
+    <t>PMP.111292.65292</t>
+  </si>
+  <si>
     <t>MOHAMMAD ULUL AZMI FIRISQON</t>
   </si>
   <si>
+    <t>Specialist of Overhead Line/ Catenary Production and Repair</t>
+  </si>
+  <si>
     <t>DIMAS RIZKIANSYAH</t>
   </si>
   <si>
+    <t>Specialist of Signalling Production and Repair</t>
+  </si>
+  <si>
     <t>DENY PRATAMA</t>
   </si>
   <si>
+    <t>Specialist of Telecommunication Production and Repair</t>
+  </si>
+  <si>
+    <t>PRP.171289.00150</t>
+  </si>
+  <si>
     <t>ARDIA RAMADAN</t>
   </si>
   <si>
+    <t>Pelaksana STE Workshop Production and Repair</t>
+  </si>
+  <si>
+    <t>PRP.130198.75616</t>
+  </si>
+  <si>
     <t>ANDRE BHASKARA</t>
   </si>
   <si>
@@ -334,430 +772,49 @@
     <t>BERLIAN ADE WIJAYA</t>
   </si>
   <si>
+    <t>Teknisi STE Workshop Production and Repair (TSSS.3)</t>
+  </si>
+  <si>
+    <t>PRP.030699.58055</t>
+  </si>
+  <si>
     <t>DWIVO ARESTU YENDRIAL</t>
   </si>
   <si>
     <t>REHAN PRASEPTIO</t>
   </si>
   <si>
+    <t>PRP.100996.72029</t>
+  </si>
+  <si>
     <t>HADI SURYONO</t>
   </si>
   <si>
+    <t>AM of STE Workshop Quality Control (TSSS.4)</t>
+  </si>
+  <si>
+    <t>PMP.090172.01057</t>
+  </si>
+  <si>
     <t>HELMY NOVIAN EKAPUTRA</t>
   </si>
   <si>
+    <t>Specialist of Testing and Evaluation</t>
+  </si>
+  <si>
+    <t>PRP.111192.117822</t>
+  </si>
+  <si>
     <t>NAFI KURNIA HARIYADI</t>
   </si>
   <si>
+    <t>Pelaksana STE Workshop Quality Control (TSSS.4)</t>
+  </si>
+  <si>
     <t>IQDAMIL JIHAD</t>
   </si>
   <si>
-    <t>Ass Manager</t>
-  </si>
-  <si>
-    <t>Executive Vice President</t>
-  </si>
-  <si>
-    <t>Vice President</t>
-  </si>
-  <si>
-    <t>Calon Pekerja</t>
-  </si>
-  <si>
-    <t>Kepala UPT BYST</t>
-  </si>
-  <si>
-    <t>Assistant Manager</t>
-  </si>
-  <si>
-    <t>Pelaksana Workshop</t>
-  </si>
-  <si>
-    <t>Calon Teknisi</t>
-  </si>
-  <si>
-    <t>Teknisi</t>
-  </si>
-  <si>
-    <t>EVP Signalling,Telecomunication, and Electricity (TS)</t>
-  </si>
-  <si>
-    <t>VP Telecommunication and Electricity Maintenance (TSC)</t>
-  </si>
-  <si>
-    <t>VP Signalling Maintenance (TSM)</t>
-  </si>
-  <si>
-    <t>Manager Overhead Catenary and Thrid Rail Maintenance (TSCC)</t>
-  </si>
-  <si>
-    <t>Specialist of Overhead Catenary Maintenance (TSCC.1)</t>
-  </si>
-  <si>
-    <t>Specialist of Third Rail Maintenance (TSCC.2)</t>
-  </si>
-  <si>
-    <t>Pelaksana Overhead Catenary Maintenance (TSCC.1)</t>
-  </si>
-  <si>
-    <t>Manager Telecomunication Network Maintenance (TSCN)</t>
-  </si>
-  <si>
-    <t>Specialist of Transmission Network Maintenance (TSCN.1)</t>
-  </si>
-  <si>
-    <t>PLT Specialist of Transmission Network Maintenance (TSCN.2)</t>
-  </si>
-  <si>
-    <t>Manager Substantion and Power Supply Maintenance (TSCP)</t>
-  </si>
-  <si>
-    <t>Specialist of Substation Maintenance (TSCP.1)</t>
-  </si>
-  <si>
-    <t>Specialist of Control Power Supply Maintenance (TSCP.2)</t>
-  </si>
-  <si>
-    <t>Pelaksana Substation and Power Supply Maintenance</t>
-  </si>
-  <si>
-    <t>Manager Telecommunication System Maintenance (TSCS)</t>
-  </si>
-  <si>
-    <t>Specialist of Railway Operation Telephone Maintenance (TSCS.1)</t>
-  </si>
-  <si>
-    <t>Specialist of Train Dispatching Maintenance (TSCS.2)</t>
-  </si>
-  <si>
-    <t>Pelaksana Railway Operation Telephone Maintenance (TSCS.1)</t>
-  </si>
-  <si>
-    <t>Pelaksana Train Dispatching Maintenance (TSCS.2)</t>
-  </si>
-  <si>
-    <t>Manager Electrical Signalling Maintenance (TSME)</t>
-  </si>
-  <si>
-    <t>Specialist of Indoor Electrical Signalling Maintenance (TSME.1)</t>
-  </si>
-  <si>
-    <t>Specialist of Outdoor Electrical Signalling Maintenance (TSME.2)</t>
-  </si>
-  <si>
-    <t>Pelaksana Indoor Electrical Signalling Maintenance</t>
-  </si>
-  <si>
-    <t>Manager Mechanical Signalling Maintenance (TSMM)</t>
-  </si>
-  <si>
-    <t>PLT Specialist of Indoor Mechanical Signalling Maintenance (TSMM.1)</t>
-  </si>
-  <si>
-    <t>PLT Specialist of Outdoor Mechanical Signalling Maintenance (TSMM.2)</t>
-  </si>
-  <si>
-    <t>Pelaksana Indoor Mechanical Signalling Maintenance</t>
-  </si>
-  <si>
-    <t>Manager Train Control Maintenance (TSMT)</t>
-  </si>
-  <si>
-    <t>Specialist of Onboard Equipment Maintenance (TSMT.1)</t>
-  </si>
-  <si>
-    <t>Specialist of Train Supervisory Maintenance (TSMT.2)</t>
-  </si>
-  <si>
-    <t>Manager Wayside Equipment Maintenance (TSMW)</t>
-  </si>
-  <si>
-    <t>Specialist of Trackside ATP/ATO Maintenance (TSMW.1)</t>
-  </si>
-  <si>
-    <t>Specialist of Trackside To Train Communication Maintenance (TSMW.2)</t>
-  </si>
-  <si>
-    <t>Pelaksana Trackside ATP/ATO Maintenance (TSMW.1)</t>
-  </si>
-  <si>
-    <t>Manager STE Program, Budgeting, Evaluation and Technical Support (TSSP)</t>
-  </si>
-  <si>
-    <t>Specialist of STE Program and Administration (TSSP.1)</t>
-  </si>
-  <si>
-    <t>Specialist of STE Budgeting and Procurement (TSSP.2)</t>
-  </si>
-  <si>
-    <t>Specialist of STE Evaluation (TSSP.3)</t>
-  </si>
-  <si>
-    <t>Specialist of STE Technical Support (TSSP.4)</t>
-  </si>
-  <si>
-    <t>Pelaksana STE Program and Administration (TSSP.1)</t>
-  </si>
-  <si>
-    <t>Pelaksana STE Evaluation (TSSP.3)</t>
-  </si>
-  <si>
-    <t>Pelaksana STE Budgeting and Procurement (TSSP.2)</t>
-  </si>
-  <si>
-    <t>Kepala UPT Balai Yasa Sintelis dan LAA Kiaracondong (TSSS)</t>
-  </si>
-  <si>
-    <t>Specialist of Hardware, Software and Integration Analysis</t>
-  </si>
-  <si>
-    <t>Specialist of Tools Calibration</t>
-  </si>
-  <si>
-    <t>AM of STE Workshop Planning and Administration (TSSS.1)</t>
-  </si>
-  <si>
-    <t>Specialist Tools and Facility</t>
-  </si>
-  <si>
-    <t>Pelaksana STE Workshop Planning and Administration (TSSS.1)</t>
-  </si>
-  <si>
-    <t>AM STE Workshop Engineering (TSSS.2)</t>
-  </si>
-  <si>
-    <t>Specialist of Overhead Line/ Catenary Engineering</t>
-  </si>
-  <si>
-    <t>Specialist of Signal Engineering</t>
-  </si>
-  <si>
-    <t>Specialist of Telecommunication Engineering</t>
-  </si>
-  <si>
-    <t>Pelaksana STE Workshop Engineering (TSSS.2)</t>
-  </si>
-  <si>
-    <t>PLT AM STE Workshop Production and Repair (TSSS.3)</t>
-  </si>
-  <si>
-    <t>Specialist of Overhead Line/ Catenary Production and Repair</t>
-  </si>
-  <si>
-    <t>Specialist of Signalling Production and Repair</t>
-  </si>
-  <si>
-    <t>Specialist of Telecommunication Production and Repair</t>
-  </si>
-  <si>
-    <t>Pelaksana STE Workshop Production and Repair</t>
-  </si>
-  <si>
-    <t>Teknisi STE Workshop Production and Repair (TSSS.3)</t>
-  </si>
-  <si>
-    <t>AM of STE Workshop Quality Control (TSSS.4)</t>
-  </si>
-  <si>
-    <t>Specialist of Testing and Evaluation</t>
-  </si>
-  <si>
-    <t>Pelaksana STE Workshop Quality Control (TSSS.4)</t>
-  </si>
-  <si>
-    <t>Kantor</t>
-  </si>
-  <si>
-    <t>16 Des 2025</t>
-  </si>
-  <si>
-    <t>1 Des 2024</t>
-  </si>
-  <si>
-    <t>1 Okt 2023</t>
-  </si>
-  <si>
-    <t>11 Okt 2019</t>
-  </si>
-  <si>
-    <t>10 Mei 2025</t>
-  </si>
-  <si>
-    <t>PMP. 161074. 00878</t>
-  </si>
-  <si>
-    <t>PMP.261079.125961</t>
-  </si>
-  <si>
-    <t>PMP.041085.00869</t>
-  </si>
-  <si>
-    <t>PMP.231071.67651</t>
-  </si>
-  <si>
-    <t>PMP. 270588. 127093</t>
-  </si>
-  <si>
-    <t>PRP.180288.39320</t>
-  </si>
-  <si>
-    <t>PMP.280576.01283</t>
-  </si>
-  <si>
-    <t>PRP.060284.57973</t>
-  </si>
-  <si>
-    <t>PRP.070474.126088</t>
-  </si>
-  <si>
-    <t>PMP. 070477. 00838</t>
-  </si>
-  <si>
-    <t>PMP.110673.127376</t>
-  </si>
-  <si>
-    <t>PMP.110889.40742</t>
-  </si>
-  <si>
-    <t>PMP.140777.128535</t>
-  </si>
-  <si>
-    <t>PMP. 101274. 125819</t>
-  </si>
-  <si>
-    <t>PRP.100391.125963</t>
-  </si>
-  <si>
-    <t>PRP.100893.38595</t>
-  </si>
-  <si>
-    <t>PRP.181094.38981</t>
-  </si>
-  <si>
-    <t>PMP. 200174. 00894</t>
-  </si>
-  <si>
-    <t>PMP. 110776. 123670</t>
-  </si>
-  <si>
-    <t>PMP.070178.00892</t>
-  </si>
-  <si>
-    <t>PRP.040272.57047</t>
-  </si>
-  <si>
-    <t>PMP.051176.00857</t>
-  </si>
-  <si>
-    <t>PMP. 151289. 125650</t>
-  </si>
-  <si>
-    <t>PMP. 160388. 126614</t>
-  </si>
-  <si>
-    <t>PMP.250376.00835</t>
-  </si>
-  <si>
-    <t>PRP.190977.38954</t>
-  </si>
-  <si>
-    <t>PMP. 100187. 00867</t>
-  </si>
-  <si>
-    <t>PMP.240573.128282</t>
-  </si>
-  <si>
-    <t>PMP.080790.125984</t>
-  </si>
-  <si>
-    <t>PMP. 010789. 126615</t>
-  </si>
-  <si>
-    <t>PMP. 080590. 125836</t>
-  </si>
-  <si>
-    <t>PMP. 060686. 01069</t>
-  </si>
-  <si>
-    <t>PRP.230298.64267</t>
-  </si>
-  <si>
-    <t>PRP. 250990. 127122</t>
-  </si>
-  <si>
-    <t>PRP.08091993.36450</t>
-  </si>
-  <si>
-    <t>PRP.191295.47000</t>
-  </si>
-  <si>
-    <t>PRP.210594.39321</t>
-  </si>
-  <si>
-    <t>PRP.120599.66072</t>
-  </si>
-  <si>
-    <t>PRP.280296.72027</t>
-  </si>
-  <si>
-    <t>PRP.040797.74257</t>
-  </si>
-  <si>
-    <t>PRP.111292.41348</t>
-  </si>
-  <si>
-    <t>PRP.171289.00150</t>
-  </si>
-  <si>
-    <t>PRP.130198.75616</t>
-  </si>
-  <si>
-    <t>PRP.030699.58055</t>
-  </si>
-  <si>
-    <t>PRP.100996.72029</t>
-  </si>
-  <si>
-    <t>PMP.090172.01057</t>
-  </si>
-  <si>
-    <t>PRP.111192.117822</t>
-  </si>
-  <si>
     <t>PRP.210695.73676</t>
-  </si>
-  <si>
-    <t>PMP.070477.00838</t>
-  </si>
-  <si>
-    <t>PMP.101274.125819</t>
-  </si>
-  <si>
-    <t>PMP.200174.00894</t>
-  </si>
-  <si>
-    <t>PMP.040272.67721</t>
-  </si>
-  <si>
-    <t>PMP.180577.00831</t>
-  </si>
-  <si>
-    <t>PMP.250376.75602</t>
-  </si>
-  <si>
-    <t>PMP.080590.125836</t>
-  </si>
-  <si>
-    <t>PMP.020478.00952</t>
-  </si>
-  <si>
-    <t>PMP.111292.65292</t>
-  </si>
-  <si>
-    <t>NIPP</t>
-  </si>
-  <si>
-    <t>TMT Pe+N1:T1</t>
   </si>
 </sst>
 </file>
@@ -828,9 +885,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -839,8 +893,11 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1144,30 +1201,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T74"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="13.15" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:T200"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="13.15" zeroHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.86328125" style="2" customWidth="1"/>
     <col min="2" max="2" width="27.265625" style="3" customWidth="1"/>
     <col min="3" max="3" width="7.86328125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="20.59765625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="20.59765625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="32" style="4" customWidth="1"/>
-    <col min="7" max="7" width="8.46484375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.1328125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="20.59765625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="21.53125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="32" style="7" customWidth="1"/>
+    <col min="7" max="7" width="12.1328125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.1328125" style="5" customWidth="1"/>
     <col min="9" max="9" width="7.06640625" style="2" customWidth="1"/>
     <col min="10" max="10" width="10.73046875" style="2" customWidth="1"/>
-    <col min="11" max="13" width="13.1328125" style="6" customWidth="1"/>
+    <col min="11" max="13" width="13.1328125" style="5" customWidth="1"/>
     <col min="14" max="14" width="22" style="2" customWidth="1"/>
-    <col min="15" max="15" width="13.1328125" style="6" customWidth="1"/>
-    <col min="16" max="16" width="22" style="3" customWidth="1"/>
-    <col min="17" max="17" width="22" style="2" customWidth="1"/>
-    <col min="18" max="18" width="13.1328125" style="6" customWidth="1"/>
-    <col min="19" max="20" width="22" style="3" customWidth="1"/>
+    <col min="15" max="15" width="13.1328125" style="5" customWidth="1"/>
+    <col min="16" max="17" width="22" style="2" customWidth="1"/>
+    <col min="18" max="18" width="13.1328125" style="5" customWidth="1"/>
+    <col min="19" max="20" width="22" style="2" customWidth="1"/>
     <col min="21" max="16384" width="9.06640625" style="3" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="5" customFormat="1" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:20" s="4" customFormat="1" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1175,7 +1231,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>242</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -1189,7 +1245,7 @@
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="6" t="s">
         <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -1198,19 +1254,19 @@
       <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="6" t="s">
         <v>11</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="6" t="s">
         <v>13</v>
       </c>
       <c r="P1" s="1" t="s">
@@ -1219,7 +1275,7 @@
       <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="7" t="s">
+      <c r="R1" s="6" t="s">
         <v>16</v>
       </c>
       <c r="S1" s="1" t="s">
@@ -1231,10 +1287,10 @@
     </row>
     <row r="2" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="C2" s="2">
         <v>41005</v>
@@ -1243,15 +1299,15 @@
         <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>117</v>
+        <v>70</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H2" s="6">
+        <v>36</v>
+      </c>
+      <c r="H2" s="5">
         <v>45988</v>
       </c>
       <c r="I2" s="2">
@@ -1260,28 +1316,22 @@
       <c r="J2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="5">
         <v>34274</v>
       </c>
-      <c r="L2" s="6">
+      <c r="L2" s="5">
         <v>27318</v>
       </c>
-      <c r="M2" s="6">
+      <c r="M2" s="5">
         <v>47788</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="O2" s="6">
-        <v>45617</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="C3" s="2">
         <v>46992</v>
@@ -1290,15 +1340,15 @@
         <v>21</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>118</v>
+        <v>79</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>85</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H3" s="6">
+        <v>36</v>
+      </c>
+      <c r="H3" s="5">
         <v>45988</v>
       </c>
       <c r="I3" s="2">
@@ -1307,34 +1357,31 @@
       <c r="J3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="5">
         <v>36586</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="5">
         <v>29154</v>
       </c>
-      <c r="M3" s="6">
+      <c r="M3" s="5">
         <v>49614</v>
       </c>
-      <c r="N3" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="O3" s="6">
+      <c r="Q3" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="R3" s="5">
         <v>47005</v>
       </c>
-      <c r="Q3" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="R3" s="6">
-        <v>47005</v>
+      <c r="S3" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>37</v>
+        <v>87</v>
       </c>
       <c r="C4" s="2">
         <v>46960</v>
@@ -1343,15 +1390,15 @@
         <v>21</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>119</v>
+        <v>79</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>88</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H4" s="6">
+        <v>36</v>
+      </c>
+      <c r="H4" s="5">
         <v>45604</v>
       </c>
       <c r="I4" s="2">
@@ -1360,22 +1407,22 @@
       <c r="J4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="5">
         <v>36586</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="5">
         <v>26911</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="5">
         <v>47392</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="C5" s="2">
         <v>50599</v>
@@ -1386,13 +1433,13 @@
       <c r="E5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>120</v>
+      <c r="F5" s="7" t="s">
+        <v>90</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H5" s="6">
+        <v>36</v>
+      </c>
+      <c r="H5" s="5">
         <v>44501</v>
       </c>
       <c r="I5" s="2">
@@ -1401,34 +1448,31 @@
       <c r="J5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="5">
         <v>39845</v>
       </c>
-      <c r="L5" s="6">
+      <c r="L5" s="5">
         <v>31324</v>
       </c>
-      <c r="M5" s="6">
+      <c r="M5" s="5">
         <v>51806</v>
       </c>
-      <c r="N5" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="O5" s="6">
-        <v>45740</v>
-      </c>
       <c r="Q5" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="R5" s="6">
+        <v>91</v>
+      </c>
+      <c r="R5" s="5">
         <v>47324</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="C6" s="2">
         <v>42218</v>
@@ -1439,13 +1483,13 @@
       <c r="E6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>121</v>
+      <c r="F6" s="7" t="s">
+        <v>93</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H6" s="6">
+        <v>36</v>
+      </c>
+      <c r="H6" s="5">
         <v>45809</v>
       </c>
       <c r="I6" s="2">
@@ -1454,34 +1498,31 @@
       <c r="J6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="5">
         <v>34669</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="5">
         <v>26229</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="5">
         <v>46692</v>
       </c>
-      <c r="N6" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="O6" s="6">
+      <c r="Q6" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="R6" s="5">
         <v>47114</v>
       </c>
-      <c r="Q6" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="R6" s="6">
-        <v>47114</v>
+      <c r="S6" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="C7" s="2">
         <v>58167</v>
@@ -1492,13 +1533,13 @@
       <c r="E7" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>122</v>
+      <c r="F7" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H7" s="6">
+        <v>36</v>
+      </c>
+      <c r="H7" s="5">
         <v>44851</v>
       </c>
       <c r="I7" s="2">
@@ -1507,34 +1548,22 @@
       <c r="J7" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="5">
         <v>40269</v>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="5">
         <v>32290</v>
       </c>
-      <c r="M7" s="6">
+      <c r="M7" s="5">
         <v>52749</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="O7" s="6">
-        <v>45693</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="R7" s="6">
-        <v>45693</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="C8" s="2">
         <v>77294</v>
@@ -1545,13 +1574,13 @@
       <c r="E8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>123</v>
+      <c r="F8" s="7" t="s">
+        <v>98</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H8" s="6">
+        <v>36</v>
+      </c>
+      <c r="H8" s="5">
         <v>45748</v>
       </c>
       <c r="I8" s="2">
@@ -1560,22 +1589,22 @@
       <c r="J8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="5">
         <v>45642</v>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="5">
         <v>36980</v>
       </c>
-      <c r="M8" s="6">
+      <c r="M8" s="5">
         <v>57436</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="C9" s="2">
         <v>69148</v>
@@ -1586,13 +1615,13 @@
       <c r="E9" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>123</v>
+      <c r="F9" s="7" t="s">
+        <v>98</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H9" s="6">
+        <v>36</v>
+      </c>
+      <c r="H9" s="5">
         <v>43721</v>
       </c>
       <c r="I9" s="2">
@@ -1601,28 +1630,31 @@
       <c r="J9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="5">
         <v>42562</v>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="5">
         <v>32191</v>
       </c>
-      <c r="M9" s="6">
+      <c r="M9" s="5">
         <v>52657</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="O9" s="6">
+        <v>100</v>
+      </c>
+      <c r="O9" s="5">
         <v>46446</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>43</v>
+        <v>101</v>
       </c>
       <c r="C10" s="2">
         <v>43891</v>
@@ -1633,13 +1665,13 @@
       <c r="E10" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>124</v>
+      <c r="F10" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H10" s="6">
+        <v>36</v>
+      </c>
+      <c r="H10" s="5">
         <v>45082</v>
       </c>
       <c r="I10" s="2">
@@ -1648,34 +1680,31 @@
       <c r="J10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="5">
         <v>35217</v>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="5">
         <v>27908</v>
       </c>
-      <c r="M10" s="6">
+      <c r="M10" s="5">
         <v>48366</v>
       </c>
-      <c r="N10" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="O10" s="6">
+      <c r="Q10" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="R10" s="5">
         <v>46208</v>
       </c>
-      <c r="Q10" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="R10" s="6">
-        <v>46208</v>
+      <c r="S10" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>44</v>
+        <v>104</v>
       </c>
       <c r="C11" s="2">
         <v>69740</v>
@@ -1686,13 +1715,13 @@
       <c r="E11" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>125</v>
+      <c r="F11" s="7" t="s">
+        <v>105</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H11" s="6">
+        <v>36</v>
+      </c>
+      <c r="H11" s="5">
         <v>45163</v>
       </c>
       <c r="I11" s="2">
@@ -1701,28 +1730,31 @@
       <c r="J11" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K11" s="6">
+      <c r="K11" s="5">
         <v>42562</v>
       </c>
-      <c r="L11" s="6">
+      <c r="L11" s="5">
         <v>30718</v>
       </c>
-      <c r="M11" s="6">
+      <c r="M11" s="5">
         <v>51196</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="O11" s="6">
+        <v>106</v>
+      </c>
+      <c r="O11" s="5">
         <v>46937</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>45</v>
+        <v>107</v>
       </c>
       <c r="C12" s="2">
         <v>43816</v>
@@ -1733,13 +1765,13 @@
       <c r="E12" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>126</v>
+      <c r="F12" s="7" t="s">
+        <v>108</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H12" s="6">
+        <v>36</v>
+      </c>
+      <c r="H12" s="5">
         <v>45945</v>
       </c>
       <c r="I12" s="2">
@@ -1748,34 +1780,31 @@
       <c r="J12" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K12" s="6">
+      <c r="K12" s="5">
         <v>35217</v>
       </c>
-      <c r="L12" s="6">
+      <c r="L12" s="5">
         <v>27126</v>
       </c>
-      <c r="M12" s="6">
-        <v>43952</v>
+      <c r="M12" s="5">
+        <v>47604</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="O12" s="6">
+        <v>109</v>
+      </c>
+      <c r="O12" s="5">
         <v>47110</v>
       </c>
-      <c r="Q12" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="R12" s="6">
-        <v>47114</v>
+      <c r="P12" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>46</v>
+        <v>110</v>
       </c>
       <c r="C13" s="2">
         <v>45493</v>
@@ -1786,13 +1815,13 @@
       <c r="E13" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>127</v>
+      <c r="F13" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H13" s="6">
+        <v>36</v>
+      </c>
+      <c r="H13" s="5">
         <v>45352</v>
       </c>
       <c r="I13" s="2">
@@ -1801,34 +1830,31 @@
       <c r="J13" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K13" s="6">
+      <c r="K13" s="5">
         <v>35339</v>
       </c>
-      <c r="L13" s="6">
+      <c r="L13" s="5">
         <v>28222</v>
       </c>
-      <c r="M13" s="6">
-        <v>44682</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="O13" s="6">
-        <v>45606</v>
+      <c r="M13" s="5">
+        <v>48700</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="R13" s="6">
+        <v>112</v>
+      </c>
+      <c r="R13" s="5">
         <v>47285</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>47</v>
+        <v>113</v>
       </c>
       <c r="C14" s="2">
         <v>43797</v>
@@ -1839,13 +1865,13 @@
       <c r="E14" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>128</v>
+      <c r="F14" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H14" s="6">
+        <v>36</v>
+      </c>
+      <c r="H14" s="5">
         <v>44805</v>
       </c>
       <c r="I14" s="2">
@@ -1854,34 +1880,22 @@
       <c r="J14" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="5">
         <v>35217</v>
       </c>
-      <c r="L14" s="6">
+      <c r="L14" s="5">
         <v>26826</v>
       </c>
-      <c r="M14" s="6">
+      <c r="M14" s="5">
         <v>47300</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="O14" s="6">
-        <v>45740</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="R14" s="6">
-        <v>45740</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>48</v>
+        <v>115</v>
       </c>
       <c r="C15" s="2">
         <v>62002</v>
@@ -1892,13 +1906,13 @@
       <c r="E15" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F15" s="4" t="s">
-        <v>129</v>
+      <c r="F15" s="7" t="s">
+        <v>116</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H15" s="6">
+        <v>36</v>
+      </c>
+      <c r="H15" s="5">
         <v>45108</v>
       </c>
       <c r="I15" s="2">
@@ -1907,34 +1921,31 @@
       <c r="J15" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K15" s="6">
+      <c r="K15" s="5">
         <v>41153</v>
       </c>
-      <c r="L15" s="6">
+      <c r="L15" s="5">
         <v>32731</v>
       </c>
-      <c r="M15" s="6">
+      <c r="M15" s="5">
         <v>53206</v>
       </c>
-      <c r="N15" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="O15" s="6">
+      <c r="Q15" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="R15" s="5">
         <v>46433</v>
       </c>
-      <c r="Q15" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="R15" s="6">
-        <v>46433</v>
+      <c r="S15" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>49</v>
+        <v>118</v>
       </c>
       <c r="C16" s="2">
         <v>78130</v>
@@ -1943,16 +1954,16 @@
         <v>33</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>130</v>
+        <v>65</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>119</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>180</v>
+        <v>36</v>
+      </c>
+      <c r="H16" s="5">
+        <v>46007</v>
       </c>
       <c r="I16" s="2">
         <v>4</v>
@@ -1960,22 +1971,22 @@
       <c r="J16" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K16" s="6">
+      <c r="K16" s="5">
         <v>46007</v>
       </c>
-      <c r="L16" s="6">
-        <v>46084</v>
-      </c>
-      <c r="M16" s="6">
-        <v>56980</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="L16" s="5">
+        <v>46007</v>
+      </c>
+      <c r="M16" s="5">
+        <v>66477</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="C17" s="2">
         <v>45497</v>
@@ -1986,14 +1997,14 @@
       <c r="E17" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>131</v>
+      <c r="F17" s="7" t="s">
+        <v>121</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>181</v>
+        <v>36</v>
+      </c>
+      <c r="H17" s="5">
+        <v>45627</v>
       </c>
       <c r="I17" s="2">
         <v>13</v>
@@ -2001,34 +2012,22 @@
       <c r="J17" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K17" s="6">
+      <c r="K17" s="5">
         <v>35339</v>
       </c>
-      <c r="L17" s="6">
+      <c r="L17" s="5">
         <v>28320</v>
       </c>
-      <c r="M17" s="6">
+      <c r="M17" s="5">
         <v>48792</v>
       </c>
-      <c r="N17" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="O17" s="6">
-        <v>45765</v>
-      </c>
-      <c r="Q17" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="R17" s="6">
-        <v>45765</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+    </row>
+    <row r="18" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>51</v>
+        <v>122</v>
       </c>
       <c r="C18" s="2">
         <v>44298</v>
@@ -2039,13 +2038,13 @@
       <c r="E18" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F18" s="4" t="s">
-        <v>132</v>
+      <c r="F18" s="7" t="s">
+        <v>123</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H18" s="6">
+        <v>36</v>
+      </c>
+      <c r="H18" s="5">
         <v>44743</v>
       </c>
       <c r="I18" s="2">
@@ -2054,34 +2053,31 @@
       <c r="J18" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K18" s="6">
+      <c r="K18" s="5">
         <v>35217</v>
       </c>
-      <c r="L18" s="6">
+      <c r="L18" s="5">
         <v>27373</v>
       </c>
-      <c r="M18" s="6">
+      <c r="M18" s="5">
         <v>47849</v>
       </c>
-      <c r="N18" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="O18" s="6">
-        <v>45646</v>
-      </c>
       <c r="Q18" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="R18" s="6">
+        <v>124</v>
+      </c>
+      <c r="R18" s="5">
         <v>47370</v>
       </c>
-    </row>
-    <row r="19" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="S18" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>52</v>
+        <v>125</v>
       </c>
       <c r="C19" s="2">
         <v>62962</v>
@@ -2092,13 +2088,13 @@
       <c r="E19" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F19" s="4" t="s">
-        <v>133</v>
+      <c r="F19" s="7" t="s">
+        <v>126</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H19" s="6">
+        <v>36</v>
+      </c>
+      <c r="H19" s="5">
         <v>45550</v>
       </c>
       <c r="I19" s="2">
@@ -2107,28 +2103,31 @@
       <c r="J19" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K19" s="6">
+      <c r="K19" s="5">
         <v>41456</v>
       </c>
-      <c r="L19" s="6">
+      <c r="L19" s="5">
         <v>33307</v>
       </c>
-      <c r="M19" s="6">
+      <c r="M19" s="5">
         <v>53783</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="O19" s="6">
+        <v>127</v>
+      </c>
+      <c r="O19" s="5">
         <v>46951</v>
       </c>
-    </row>
-    <row r="20" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P19" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="C20" s="2">
         <v>70252</v>
@@ -2139,14 +2138,14 @@
       <c r="E20" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F20" s="4" t="s">
-        <v>134</v>
+      <c r="F20" s="7" t="s">
+        <v>129</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>182</v>
+        <v>36</v>
+      </c>
+      <c r="H20" s="5">
+        <v>45200</v>
       </c>
       <c r="I20" s="2">
         <v>4</v>
@@ -2154,28 +2153,31 @@
       <c r="J20" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K20" s="6">
+      <c r="K20" s="5">
         <v>42675</v>
       </c>
-      <c r="L20" s="6">
+      <c r="L20" s="5">
         <v>34191</v>
       </c>
-      <c r="M20" s="6">
+      <c r="M20" s="5">
         <v>54667</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="O20" s="6">
+        <v>130</v>
+      </c>
+      <c r="O20" s="5">
         <v>46407</v>
       </c>
-    </row>
-    <row r="21" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P20" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>54</v>
+        <v>131</v>
       </c>
       <c r="C21" s="2">
         <v>70628</v>
@@ -2186,14 +2188,14 @@
       <c r="E21" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>135</v>
+      <c r="F21" s="7" t="s">
+        <v>132</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>183</v>
+        <v>36</v>
+      </c>
+      <c r="H21" s="5">
+        <v>43749</v>
       </c>
       <c r="I21" s="2">
         <v>4</v>
@@ -2201,28 +2203,31 @@
       <c r="J21" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K21" s="6">
+      <c r="K21" s="5">
         <v>42725</v>
       </c>
-      <c r="L21" s="6">
+      <c r="L21" s="5">
         <v>34625</v>
       </c>
-      <c r="M21" s="6">
+      <c r="M21" s="5">
         <v>55093</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="O21" s="6">
+        <v>133</v>
+      </c>
+      <c r="O21" s="5">
         <v>46407</v>
       </c>
-    </row>
-    <row r="22" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P21" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>55</v>
+        <v>134</v>
       </c>
       <c r="C22" s="2">
         <v>77293</v>
@@ -2233,13 +2238,13 @@
       <c r="E22" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F22" s="4" t="s">
-        <v>135</v>
+      <c r="F22" s="7" t="s">
+        <v>132</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H22" s="6">
+        <v>36</v>
+      </c>
+      <c r="H22" s="5">
         <v>45748</v>
       </c>
       <c r="I22" s="2">
@@ -2248,22 +2253,22 @@
       <c r="J22" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K22" s="6">
+      <c r="K22" s="5">
         <v>45642</v>
       </c>
-      <c r="L22" s="6">
-        <v>36879</v>
-      </c>
-      <c r="M22" s="6">
+      <c r="L22" s="5">
+        <v>36889</v>
+      </c>
+      <c r="M22" s="5">
         <v>57346</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>56</v>
+        <v>135</v>
       </c>
       <c r="C23" s="2">
         <v>42007</v>
@@ -2274,14 +2279,14 @@
       <c r="E23" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="7" t="s">
         <v>136</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>184</v>
+        <v>36</v>
+      </c>
+      <c r="H23" s="5">
+        <v>45787</v>
       </c>
       <c r="I23" s="2">
         <v>13</v>
@@ -2289,34 +2294,31 @@
       <c r="J23" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K23" s="6">
+      <c r="K23" s="5">
         <v>34669</v>
       </c>
-      <c r="L23" s="6">
+      <c r="L23" s="5">
         <v>27049</v>
       </c>
-      <c r="M23" s="6">
+      <c r="M23" s="5">
         <v>47515</v>
       </c>
-      <c r="N23" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="O23" s="6">
-        <v>45635</v>
-      </c>
       <c r="Q23" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="R23" s="6">
+        <v>137</v>
+      </c>
+      <c r="R23" s="5">
         <v>47265</v>
       </c>
-    </row>
-    <row r="24" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="S23" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>27</v>
@@ -2324,25 +2326,22 @@
       <c r="E24" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="4" t="s">
-        <v>137</v>
+      <c r="F24" s="7" t="s">
+        <v>138</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H24" s="6">
-        <v>46054</v>
+        <v>36</v>
       </c>
       <c r="I24" s="2">
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A25" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>58</v>
+        <v>139</v>
       </c>
       <c r="C25" s="2">
         <v>43894</v>
@@ -2353,13 +2352,13 @@
       <c r="E25" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F25" s="4" t="s">
-        <v>138</v>
+      <c r="F25" s="7" t="s">
+        <v>140</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H25" s="6">
+        <v>36</v>
+      </c>
+      <c r="H25" s="5">
         <v>44743</v>
       </c>
       <c r="I25" s="2">
@@ -2368,28 +2367,22 @@
       <c r="J25" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K25" s="6">
+      <c r="K25" s="5">
         <v>35217</v>
       </c>
-      <c r="L25" s="6">
+      <c r="L25" s="5">
         <v>27952</v>
       </c>
-      <c r="M25" s="6">
+      <c r="M25" s="5">
         <v>48427</v>
       </c>
-      <c r="N25" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="O25" s="6">
-        <v>45605</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+    </row>
+    <row r="26" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>59</v>
+        <v>141</v>
       </c>
       <c r="C26" s="2">
         <v>76197</v>
@@ -2400,13 +2393,13 @@
       <c r="E26" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F26" s="4" t="s">
-        <v>139</v>
+      <c r="F26" s="7" t="s">
+        <v>142</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H26" s="6">
+        <v>36</v>
+      </c>
+      <c r="H26" s="5">
         <v>45323</v>
       </c>
       <c r="I26" s="2">
@@ -2415,22 +2408,22 @@
       <c r="J26" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K26" s="6">
+      <c r="K26" s="5">
         <v>45200</v>
       </c>
-      <c r="L26" s="6">
+      <c r="L26" s="5">
         <v>37363</v>
       </c>
-      <c r="M26" s="6">
+      <c r="M26" s="5">
         <v>57831</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A27" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>60</v>
+        <v>143</v>
       </c>
       <c r="C27" s="2">
         <v>45912</v>
@@ -2441,13 +2434,13 @@
       <c r="E27" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F27" s="4" t="s">
-        <v>140</v>
+      <c r="F27" s="7" t="s">
+        <v>144</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H27" s="6">
+        <v>36</v>
+      </c>
+      <c r="H27" s="5">
         <v>45809</v>
       </c>
       <c r="I27" s="2">
@@ -2456,34 +2449,31 @@
       <c r="J27" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K27" s="6">
+      <c r="K27" s="5">
         <v>35490</v>
       </c>
-      <c r="L27" s="6">
+      <c r="L27" s="5">
         <v>28497</v>
       </c>
-      <c r="M27" s="6">
+      <c r="M27" s="5">
         <v>48976</v>
       </c>
-      <c r="N27" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="O27" s="6">
+      <c r="Q27" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="R27" s="5">
         <v>47114</v>
       </c>
-      <c r="Q27" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="R27" s="6">
-        <v>47114</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="S27" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A28" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>61</v>
+        <v>146</v>
       </c>
       <c r="C28" s="2">
         <v>69189</v>
@@ -2494,13 +2484,13 @@
       <c r="E28" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F28" s="4" t="s">
-        <v>141</v>
+      <c r="F28" s="7" t="s">
+        <v>147</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H28" s="6">
+        <v>36</v>
+      </c>
+      <c r="H28" s="5">
         <v>45992</v>
       </c>
       <c r="I28" s="2">
@@ -2509,22 +2499,40 @@
       <c r="J28" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K28" s="6">
+      <c r="K28" s="5">
         <v>42562</v>
       </c>
-      <c r="L28" s="6">
+      <c r="L28" s="5">
         <v>34211</v>
       </c>
-      <c r="M28" s="6">
+      <c r="M28" s="5">
         <v>54667</v>
       </c>
-    </row>
-    <row r="29" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="N28" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="O28" s="5">
+        <v>46481</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q28" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="R28" s="5">
+        <v>47097</v>
+      </c>
+      <c r="S28" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A29" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>62</v>
+        <v>150</v>
       </c>
       <c r="C29" s="2">
         <v>48694</v>
@@ -2535,14 +2543,14 @@
       <c r="E29" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F29" s="4" t="s">
-        <v>142</v>
+      <c r="F29" s="7" t="s">
+        <v>151</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H29" s="6">
-        <v>45870</v>
+        <v>36</v>
+      </c>
+      <c r="H29" s="5">
+        <v>45992</v>
       </c>
       <c r="I29" s="2">
         <v>11</v>
@@ -2550,37 +2558,40 @@
       <c r="J29" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K29" s="6">
+      <c r="K29" s="5">
         <v>38899</v>
       </c>
-      <c r="L29" s="6">
+      <c r="L29" s="5">
         <v>26333</v>
       </c>
-      <c r="M29" s="6">
+      <c r="M29" s="5">
         <v>46813</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="O29" s="6">
+        <v>152</v>
+      </c>
+      <c r="O29" s="5">
         <v>46916</v>
       </c>
-      <c r="P29" s="8" t="s">
-        <v>243</v>
+      <c r="P29" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="R29" s="6">
+        <v>153</v>
+      </c>
+      <c r="R29" s="5">
         <v>47110</v>
       </c>
-    </row>
-    <row r="30" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="S29" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A30" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>63</v>
+        <v>154</v>
       </c>
       <c r="C30" s="2">
         <v>76196</v>
@@ -2591,13 +2602,13 @@
       <c r="E30" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F30" s="4" t="s">
-        <v>143</v>
+      <c r="F30" s="7" t="s">
+        <v>155</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H30" s="6">
+        <v>36</v>
+      </c>
+      <c r="H30" s="5">
         <v>45323</v>
       </c>
       <c r="I30" s="2">
@@ -2606,22 +2617,22 @@
       <c r="J30" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K30" s="6">
+      <c r="K30" s="5">
         <v>45200</v>
       </c>
-      <c r="L30" s="6">
+      <c r="L30" s="5">
         <v>37354</v>
       </c>
-      <c r="M30" s="6">
+      <c r="M30" s="5">
         <v>57831</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A31" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>64</v>
+        <v>156</v>
       </c>
       <c r="C31" s="2">
         <v>45772</v>
@@ -2632,14 +2643,14 @@
       <c r="E31" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F31" s="4" t="s">
-        <v>144</v>
+      <c r="F31" s="7" t="s">
+        <v>157</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H31" s="6">
-        <v>46001</v>
+        <v>36</v>
+      </c>
+      <c r="H31" s="5">
+        <v>45870</v>
       </c>
       <c r="I31" s="2">
         <v>13</v>
@@ -2647,34 +2658,31 @@
       <c r="J31" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K31" s="6">
+      <c r="K31" s="5">
         <v>35490</v>
       </c>
-      <c r="L31" s="6">
+      <c r="L31" s="5">
         <v>27881</v>
       </c>
-      <c r="M31" s="6">
-        <v>48366</v>
-      </c>
-      <c r="N31" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="O31" s="6">
+      <c r="M31" s="5">
+        <v>48549</v>
+      </c>
+      <c r="Q31" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="R31" s="5">
         <v>47114</v>
       </c>
-      <c r="Q31" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="R31" s="6">
-        <v>47114</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="S31" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A32" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>65</v>
+        <v>159</v>
       </c>
       <c r="C32" s="2">
         <v>63015</v>
@@ -2685,13 +2693,13 @@
       <c r="E32" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F32" s="4" t="s">
-        <v>145</v>
+      <c r="F32" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H32" s="6">
+        <v>36</v>
+      </c>
+      <c r="H32" s="5">
         <v>45550</v>
       </c>
       <c r="I32" s="2">
@@ -2700,28 +2708,22 @@
       <c r="J32" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K32" s="6">
+      <c r="K32" s="5">
         <v>41487</v>
       </c>
-      <c r="L32" s="6">
+      <c r="L32" s="5">
         <v>32857</v>
       </c>
-      <c r="M32" s="6">
+      <c r="M32" s="5">
         <v>53328</v>
       </c>
-      <c r="N32" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="O32" s="6">
-        <v>45646</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+    </row>
+    <row r="33" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A33" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="C33" s="2">
         <v>58168</v>
@@ -2732,13 +2734,13 @@
       <c r="E33" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F33" s="4" t="s">
-        <v>146</v>
+      <c r="F33" s="7" t="s">
+        <v>162</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H33" s="6">
+        <v>36</v>
+      </c>
+      <c r="H33" s="5">
         <v>45992</v>
       </c>
       <c r="I33" s="2">
@@ -2747,34 +2749,22 @@
       <c r="J33" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K33" s="6">
+      <c r="K33" s="5">
         <v>40269</v>
       </c>
-      <c r="L33" s="6">
+      <c r="L33" s="5">
         <v>32218</v>
       </c>
-      <c r="M33" s="6">
+      <c r="M33" s="5">
         <v>52688</v>
       </c>
-      <c r="N33" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="O33" s="6">
-        <v>45696</v>
-      </c>
-      <c r="Q33" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="R33" s="6">
-        <v>45696</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+    </row>
+    <row r="34" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A34" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>67</v>
+        <v>163</v>
       </c>
       <c r="C34" s="2">
         <v>43914</v>
@@ -2785,13 +2775,13 @@
       <c r="E34" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F34" s="4" t="s">
-        <v>147</v>
+      <c r="F34" s="7" t="s">
+        <v>164</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H34" s="6">
+        <v>36</v>
+      </c>
+      <c r="H34" s="5">
         <v>45352</v>
       </c>
       <c r="I34" s="2">
@@ -2800,28 +2790,31 @@
       <c r="J34" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K34" s="6">
-        <v>35070</v>
-      </c>
-      <c r="L34" s="6">
+      <c r="K34" s="5">
+        <v>35217</v>
+      </c>
+      <c r="L34" s="5">
         <v>28263</v>
       </c>
-      <c r="M34" s="6">
+      <c r="M34" s="5">
         <v>48731</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="R34" s="6">
+        <v>165</v>
+      </c>
+      <c r="R34" s="5">
         <v>47324</v>
       </c>
-    </row>
-    <row r="35" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="S34" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A35" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>68</v>
+        <v>166</v>
       </c>
       <c r="C35" s="2">
         <v>43887</v>
@@ -2832,13 +2825,13 @@
       <c r="E35" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F35" s="4" t="s">
-        <v>148</v>
+      <c r="F35" s="7" t="s">
+        <v>167</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H35" s="6">
+        <v>36</v>
+      </c>
+      <c r="H35" s="5">
         <v>45627</v>
       </c>
       <c r="I35" s="2">
@@ -2847,34 +2840,31 @@
       <c r="J35" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K35" s="6">
+      <c r="K35" s="5">
         <v>35217</v>
       </c>
-      <c r="L35" s="6">
+      <c r="L35" s="5">
         <v>27844</v>
       </c>
-      <c r="M35" s="6">
+      <c r="M35" s="5">
         <v>48305</v>
       </c>
-      <c r="N35" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="O35" s="6">
-        <v>46851</v>
-      </c>
       <c r="Q35" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="R35" s="6">
+        <v>168</v>
+      </c>
+      <c r="R35" s="5">
         <v>47370</v>
       </c>
-    </row>
-    <row r="36" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="S35" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A36" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>69</v>
+        <v>169</v>
       </c>
       <c r="C36" s="2">
         <v>45506</v>
@@ -2885,14 +2875,14 @@
       <c r="E36" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F36" s="4" t="s">
-        <v>149</v>
+      <c r="F36" s="7" t="s">
+        <v>170</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H36" s="6">
-        <v>46013</v>
+        <v>36</v>
+      </c>
+      <c r="H36" s="5">
+        <v>45839</v>
       </c>
       <c r="I36" s="2">
         <v>11</v>
@@ -2900,28 +2890,31 @@
       <c r="J36" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K36" s="6">
+      <c r="K36" s="5">
         <v>35339</v>
       </c>
-      <c r="L36" s="6">
+      <c r="L36" s="5">
         <v>28387</v>
       </c>
-      <c r="M36" s="6">
+      <c r="M36" s="5">
         <v>48853</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="O36" s="6">
+        <v>171</v>
+      </c>
+      <c r="O36" s="5">
         <v>46407</v>
       </c>
-    </row>
-    <row r="37" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P36" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A37" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>70</v>
+        <v>172</v>
       </c>
       <c r="C37" s="2">
         <v>76193</v>
@@ -2932,13 +2925,13 @@
       <c r="E37" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F37" s="4" t="s">
-        <v>150</v>
+      <c r="F37" s="7" t="s">
+        <v>173</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H37" s="6">
+        <v>36</v>
+      </c>
+      <c r="H37" s="5">
         <v>45839</v>
       </c>
       <c r="I37" s="2">
@@ -2947,22 +2940,22 @@
       <c r="J37" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K37" s="6">
+      <c r="K37" s="5">
         <v>45200</v>
       </c>
-      <c r="L37" s="6">
+      <c r="L37" s="5">
         <v>36815</v>
       </c>
-      <c r="M37" s="6">
+      <c r="M37" s="5">
         <v>57285</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A38" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>71</v>
+        <v>174</v>
       </c>
       <c r="C38" s="2">
         <v>58221</v>
@@ -2973,14 +2966,14 @@
       <c r="E38" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F38" s="4" t="s">
-        <v>151</v>
+      <c r="F38" s="7" t="s">
+        <v>175</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H38" s="6">
-        <v>46001</v>
+        <v>36</v>
+      </c>
+      <c r="H38" s="5">
+        <v>45352</v>
       </c>
       <c r="I38" s="2">
         <v>13</v>
@@ -2988,34 +2981,22 @@
       <c r="J38" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K38" s="6">
+      <c r="K38" s="5">
         <v>40269</v>
       </c>
-      <c r="L38" s="6">
+      <c r="L38" s="5">
         <v>31787</v>
       </c>
-      <c r="M38" s="6">
+      <c r="M38" s="5">
         <v>52263</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="O38" s="6">
-        <v>45696</v>
-      </c>
-      <c r="Q38" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="R38" s="6">
-        <v>45696</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+    </row>
+    <row r="39" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A39" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>72</v>
+        <v>176</v>
       </c>
       <c r="C39" s="2">
         <v>44284</v>
@@ -3026,13 +3007,13 @@
       <c r="E39" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F39" s="4" t="s">
-        <v>152</v>
+      <c r="F39" s="7" t="s">
+        <v>177</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H39" s="6">
+        <v>36</v>
+      </c>
+      <c r="H39" s="5">
         <v>44805</v>
       </c>
       <c r="I39" s="2">
@@ -3041,34 +3022,31 @@
       <c r="J39" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K39" s="6">
+      <c r="K39" s="5">
         <v>35217</v>
       </c>
-      <c r="L39" s="6">
+      <c r="L39" s="5">
         <v>26808</v>
       </c>
-      <c r="M39" s="6">
+      <c r="M39" s="5">
         <v>47270</v>
       </c>
-      <c r="N39" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="O39" s="6">
-        <v>45747</v>
-      </c>
       <c r="Q39" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="R39" s="6">
+        <v>178</v>
+      </c>
+      <c r="R39" s="5">
         <v>47370</v>
       </c>
-    </row>
-    <row r="40" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="S39" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A40" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>73</v>
+        <v>179</v>
       </c>
       <c r="C40" s="2">
         <v>62951</v>
@@ -3079,13 +3057,13 @@
       <c r="E40" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F40" s="4" t="s">
-        <v>153</v>
+      <c r="F40" s="7" t="s">
+        <v>180</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H40" s="6">
+        <v>36</v>
+      </c>
+      <c r="H40" s="5">
         <v>45901</v>
       </c>
       <c r="I40" s="2">
@@ -3094,34 +3072,31 @@
       <c r="J40" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K40" s="6">
+      <c r="K40" s="5">
         <v>41456</v>
       </c>
-      <c r="L40" s="6">
+      <c r="L40" s="5">
         <v>33062</v>
       </c>
-      <c r="M40" s="6">
+      <c r="M40" s="5">
         <v>53540</v>
       </c>
-      <c r="N40" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="O40" s="6">
+      <c r="Q40" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="R40" s="5">
         <v>47005</v>
       </c>
-      <c r="Q40" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="R40" s="6">
-        <v>47005</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="S40" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A41" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>74</v>
+        <v>182</v>
       </c>
       <c r="C41" s="2">
         <v>56781</v>
@@ -3132,13 +3107,13 @@
       <c r="E41" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F41" s="4" t="s">
-        <v>154</v>
+      <c r="F41" s="7" t="s">
+        <v>183</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H41" s="6">
+        <v>36</v>
+      </c>
+      <c r="H41" s="5">
         <v>44809</v>
       </c>
       <c r="I41" s="2">
@@ -3147,34 +3122,22 @@
       <c r="J41" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K41" s="6">
+      <c r="K41" s="5">
         <v>40163</v>
       </c>
-      <c r="L41" s="6">
+      <c r="L41" s="5">
         <v>32690</v>
       </c>
-      <c r="M41" s="6">
+      <c r="M41" s="5">
         <v>53175</v>
       </c>
-      <c r="N41" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="O41" s="6">
-        <v>45696</v>
-      </c>
-      <c r="Q41" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="R41" s="6">
-        <v>45696</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+    </row>
+    <row r="42" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A42" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>75</v>
+        <v>184</v>
       </c>
       <c r="C42" s="2">
         <v>64532</v>
@@ -3185,13 +3148,13 @@
       <c r="E42" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F42" s="4" t="s">
-        <v>155</v>
+      <c r="F42" s="7" t="s">
+        <v>185</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H42" s="6">
+        <v>36</v>
+      </c>
+      <c r="H42" s="5">
         <v>45901</v>
       </c>
       <c r="I42" s="2">
@@ -3200,34 +3163,31 @@
       <c r="J42" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K42" s="6">
+      <c r="K42" s="5">
         <v>41791</v>
       </c>
-      <c r="L42" s="6">
-        <v>33000</v>
-      </c>
-      <c r="M42" s="6">
+      <c r="L42" s="5">
+        <v>33001</v>
+      </c>
+      <c r="M42" s="5">
         <v>53479</v>
       </c>
-      <c r="N42" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="O42" s="6">
-        <v>45646</v>
-      </c>
       <c r="Q42" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="R42" s="6">
+        <v>186</v>
+      </c>
+      <c r="R42" s="5">
         <v>47265</v>
       </c>
-    </row>
-    <row r="43" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="S42" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A43" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>76</v>
+        <v>187</v>
       </c>
       <c r="C43" s="2">
         <v>70627</v>
@@ -3238,14 +3198,14 @@
       <c r="E43" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F43" s="4" t="s">
-        <v>156</v>
+      <c r="F43" s="7" t="s">
+        <v>188</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H43" s="6">
-        <v>44927</v>
+        <v>36</v>
+      </c>
+      <c r="H43" s="5">
+        <v>43721</v>
       </c>
       <c r="I43" s="2">
         <v>4</v>
@@ -3253,22 +3213,22 @@
       <c r="J43" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K43" s="6">
+      <c r="K43" s="5">
         <v>42725</v>
       </c>
-      <c r="L43" s="6">
+      <c r="L43" s="5">
         <v>33753</v>
       </c>
-      <c r="M43" s="6">
+      <c r="M43" s="5">
         <v>54210</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A44" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>77</v>
+        <v>189</v>
       </c>
       <c r="C44" s="2">
         <v>74344</v>
@@ -3279,14 +3239,14 @@
       <c r="E44" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F44" s="4" t="s">
-        <v>157</v>
+      <c r="F44" s="7" t="s">
+        <v>190</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H44" s="6">
-        <v>44927</v>
+        <v>36</v>
+      </c>
+      <c r="H44" s="5">
+        <v>44866</v>
       </c>
       <c r="I44" s="2">
         <v>5</v>
@@ -3294,22 +3254,22 @@
       <c r="J44" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K44" s="6">
+      <c r="K44" s="5">
         <v>44774</v>
       </c>
-      <c r="L44" s="6">
+      <c r="L44" s="5">
         <v>35543</v>
       </c>
-      <c r="M44" s="6">
+      <c r="M44" s="5">
         <v>56005</v>
       </c>
     </row>
-    <row r="45" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A45" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>78</v>
+        <v>191</v>
       </c>
       <c r="C45" s="2">
         <v>78108</v>
@@ -3320,13 +3280,13 @@
       <c r="E45" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F45" s="4" t="s">
-        <v>158</v>
+      <c r="F45" s="7" t="s">
+        <v>192</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H45" s="6">
+        <v>36</v>
+      </c>
+      <c r="H45" s="5">
         <v>45962</v>
       </c>
       <c r="I45" s="2">
@@ -3335,22 +3295,22 @@
       <c r="J45" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K45" s="6">
+      <c r="K45" s="5">
         <v>45962</v>
       </c>
-      <c r="L45" s="6">
-        <v>46084</v>
-      </c>
-      <c r="M45" s="6">
-        <v>56980</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="L45" s="5">
+        <v>36674</v>
+      </c>
+      <c r="M45" s="5">
+        <v>57132</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A46" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>79</v>
+        <v>193</v>
       </c>
       <c r="C46" s="2">
         <v>50612</v>
@@ -3359,15 +3319,15 @@
         <v>23</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>159</v>
+        <v>71</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H46" s="6">
+        <v>36</v>
+      </c>
+      <c r="H46" s="5">
         <v>45627</v>
       </c>
       <c r="I46" s="2">
@@ -3376,34 +3336,22 @@
       <c r="J46" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K46" s="6">
+      <c r="K46" s="5">
         <v>39845</v>
       </c>
-      <c r="L46" s="6">
+      <c r="L46" s="5">
         <v>31569</v>
       </c>
-      <c r="M46" s="6">
+      <c r="M46" s="5">
         <v>52048</v>
       </c>
-      <c r="N46" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="O46" s="6">
-        <v>45740</v>
-      </c>
-      <c r="Q46" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="R46" s="6">
-        <v>45740</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+    </row>
+    <row r="47" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A47" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>80</v>
+        <v>195</v>
       </c>
       <c r="C47" s="2">
         <v>68886</v>
@@ -3414,13 +3362,13 @@
       <c r="E47" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F47" s="4" t="s">
-        <v>160</v>
+      <c r="F47" s="7" t="s">
+        <v>196</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H47" s="6">
+        <v>36</v>
+      </c>
+      <c r="H47" s="5">
         <v>45566</v>
       </c>
       <c r="I47" s="2">
@@ -3429,22 +3377,22 @@
       <c r="J47" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K47" s="6">
-        <v>42552</v>
-      </c>
-      <c r="L47" s="6">
-        <v>46084</v>
-      </c>
-      <c r="M47" s="6">
-        <v>56980</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="K47" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L47" s="5">
+        <v>32783</v>
+      </c>
+      <c r="M47" s="5">
+        <v>53267</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A48" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>81</v>
+        <v>197</v>
       </c>
       <c r="C48" s="2">
         <v>61558</v>
@@ -3455,13 +3403,13 @@
       <c r="E48" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F48" s="4" t="s">
-        <v>161</v>
+      <c r="F48" s="7" t="s">
+        <v>198</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H48" s="6">
+        <v>36</v>
+      </c>
+      <c r="H48" s="5">
         <v>45061</v>
       </c>
       <c r="I48" s="2">
@@ -3470,40 +3418,40 @@
       <c r="J48" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K48" s="6">
+      <c r="K48" s="5">
         <v>40787</v>
       </c>
-      <c r="L48" s="6">
+      <c r="L48" s="5">
         <v>34304</v>
       </c>
-      <c r="M48" s="6">
+      <c r="M48" s="5">
         <v>54789</v>
       </c>
     </row>
-    <row r="49" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A49" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="C49" s="2">
         <v>46338</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>108</v>
+        <v>34</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>162</v>
+        <v>35</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>200</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H49" s="6">
-        <v>46060</v>
+        <v>36</v>
+      </c>
+      <c r="H49" s="5">
+        <v>45627</v>
       </c>
       <c r="I49" s="2">
         <v>11</v>
@@ -3511,28 +3459,31 @@
       <c r="J49" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K49" s="6">
+      <c r="K49" s="5">
         <v>35490</v>
       </c>
-      <c r="L49" s="6">
+      <c r="L49" s="5">
         <v>28582</v>
       </c>
-      <c r="M49" s="6">
+      <c r="M49" s="5">
         <v>49065</v>
       </c>
       <c r="Q49" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="R49" s="6">
+        <v>201</v>
+      </c>
+      <c r="R49" s="5">
         <v>47265</v>
       </c>
-    </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="S49" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A50" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>83</v>
+        <v>202</v>
       </c>
       <c r="C50" s="2">
         <v>58848</v>
@@ -3543,13 +3494,13 @@
       <c r="E50" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F50" s="4" t="s">
-        <v>163</v>
+      <c r="F50" s="7" t="s">
+        <v>203</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H50" s="6">
+        <v>36</v>
+      </c>
+      <c r="H50" s="5">
         <v>44757</v>
       </c>
       <c r="I50" s="2">
@@ -3558,22 +3509,22 @@
       <c r="J50" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K50" s="6">
+      <c r="K50" s="5">
         <v>40575</v>
       </c>
-      <c r="L50" s="6">
+      <c r="L50" s="5">
         <v>30426</v>
       </c>
-      <c r="M50" s="6">
+      <c r="M50" s="5">
         <v>50891</v>
       </c>
     </row>
-    <row r="51" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A51" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>84</v>
+        <v>204</v>
       </c>
       <c r="C51" s="2">
         <v>74313</v>
@@ -3582,15 +3533,15 @@
         <v>33</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F51" s="4" t="s">
-        <v>164</v>
+        <v>72</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>205</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H51" s="6">
+        <v>36</v>
+      </c>
+      <c r="H51" s="5">
         <v>45089</v>
       </c>
       <c r="I51" s="2">
@@ -3599,45 +3550,48 @@
       <c r="J51" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K51" s="6">
+      <c r="K51" s="5">
         <v>44652</v>
       </c>
-      <c r="L51" s="6">
+      <c r="L51" s="5">
         <v>35849</v>
       </c>
-      <c r="M51" s="6">
+      <c r="M51" s="5">
         <v>56309</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="O51" s="6">
+        <v>206</v>
+      </c>
+      <c r="O51" s="5">
         <v>47005</v>
       </c>
-    </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P51" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A52" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>85</v>
+        <v>207</v>
       </c>
       <c r="C52" s="2">
         <v>44668</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>108</v>
+        <v>34</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F52" s="4" t="s">
-        <v>165</v>
+        <v>35</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>208</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H52" s="6">
+        <v>36</v>
+      </c>
+      <c r="H52" s="5">
         <v>45839</v>
       </c>
       <c r="I52" s="2">
@@ -3646,22 +3600,22 @@
       <c r="J52" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K52" s="6">
+      <c r="K52" s="5">
         <v>35217</v>
       </c>
-      <c r="L52" s="6">
+      <c r="L52" s="5">
         <v>26534</v>
       </c>
-      <c r="M52" s="6">
+      <c r="M52" s="5">
         <v>46997</v>
       </c>
     </row>
-    <row r="53" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A53" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>86</v>
+        <v>209</v>
       </c>
       <c r="C53" s="2">
         <v>64568</v>
@@ -3672,13 +3626,13 @@
       <c r="E53" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F53" s="4" t="s">
-        <v>166</v>
+      <c r="F53" s="7" t="s">
+        <v>210</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H53" s="6">
+        <v>36</v>
+      </c>
+      <c r="H53" s="5">
         <v>46060</v>
       </c>
       <c r="I53" s="2">
@@ -3687,28 +3641,22 @@
       <c r="J53" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K53" s="6">
+      <c r="K53" s="5">
         <v>41791</v>
       </c>
-      <c r="L53" s="6">
+      <c r="L53" s="5">
         <v>34230</v>
       </c>
-      <c r="M53" s="6">
+      <c r="M53" s="5">
         <v>54697</v>
       </c>
-      <c r="N53" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="O53" s="6">
-        <v>45696</v>
-      </c>
-    </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A54" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>87</v>
+        <v>211</v>
       </c>
       <c r="C54" s="2">
         <v>69525</v>
@@ -3719,13 +3667,13 @@
       <c r="E54" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F54" s="4" t="s">
-        <v>167</v>
+      <c r="F54" s="7" t="s">
+        <v>212</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H54" s="6">
+        <v>36</v>
+      </c>
+      <c r="H54" s="5">
         <v>45566</v>
       </c>
       <c r="I54" s="2">
@@ -3734,28 +3682,31 @@
       <c r="J54" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K54" s="6">
+      <c r="K54" s="5">
         <v>42548</v>
       </c>
-      <c r="L54" s="6">
+      <c r="L54" s="5">
         <v>33141</v>
       </c>
-      <c r="M54" s="6">
-        <v>53328</v>
+      <c r="M54" s="5">
+        <v>54697</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="O54" s="6">
+        <v>213</v>
+      </c>
+      <c r="O54" s="5">
         <v>46211</v>
       </c>
-    </row>
-    <row r="55" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P54" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A55" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>88</v>
+        <v>214</v>
       </c>
       <c r="C55" s="2">
         <v>68958</v>
@@ -3766,13 +3717,13 @@
       <c r="E55" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F55" s="4" t="s">
-        <v>168</v>
+      <c r="F55" s="7" t="s">
+        <v>215</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H55" s="6">
+        <v>36</v>
+      </c>
+      <c r="H55" s="5">
         <v>45731</v>
       </c>
       <c r="I55" s="2">
@@ -3781,28 +3732,31 @@
       <c r="J55" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K55" s="6">
+      <c r="K55" s="5">
         <v>42562</v>
       </c>
-      <c r="L55" s="6">
+      <c r="L55" s="5">
         <v>35052</v>
       </c>
-      <c r="M55" s="6">
+      <c r="M55" s="5">
         <v>55519</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="O55" s="6">
+        <v>216</v>
+      </c>
+      <c r="O55" s="5">
         <v>46610</v>
       </c>
-    </row>
-    <row r="56" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P55" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A56" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>89</v>
+        <v>217</v>
       </c>
       <c r="C56" s="2">
         <v>69136</v>
@@ -3813,14 +3767,14 @@
       <c r="E56" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F56" s="4" t="s">
-        <v>169</v>
+      <c r="F56" s="7" t="s">
+        <v>218</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H56" s="6">
-        <v>44927</v>
+        <v>36</v>
+      </c>
+      <c r="H56" s="5">
+        <v>43721</v>
       </c>
       <c r="I56" s="2">
         <v>4</v>
@@ -3828,28 +3782,31 @@
       <c r="J56" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K56" s="6">
+      <c r="K56" s="5">
         <v>42562</v>
       </c>
-      <c r="L56" s="6">
+      <c r="L56" s="5">
         <v>34475</v>
       </c>
-      <c r="M56" s="6">
+      <c r="M56" s="5">
         <v>54940</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="O56" s="6">
+        <v>219</v>
+      </c>
+      <c r="O56" s="5">
         <v>46446</v>
       </c>
-    </row>
-    <row r="57" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P56" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A57" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>90</v>
+        <v>220</v>
       </c>
       <c r="C57" s="2">
         <v>74904</v>
@@ -3860,13 +3817,13 @@
       <c r="E57" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F57" s="4" t="s">
-        <v>169</v>
+      <c r="F57" s="7" t="s">
+        <v>218</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H57" s="6">
+        <v>36</v>
+      </c>
+      <c r="H57" s="5">
         <v>45054</v>
       </c>
       <c r="I57" s="2">
@@ -3875,28 +3832,31 @@
       <c r="J57" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K57" s="6">
+      <c r="K57" s="5">
         <v>44866</v>
       </c>
-      <c r="L57" s="6">
+      <c r="L57" s="5">
         <v>36292</v>
       </c>
-      <c r="M57" s="6">
+      <c r="M57" s="5">
         <v>56766</v>
       </c>
       <c r="N57" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="O57" s="5">
+        <v>47054</v>
+      </c>
+      <c r="P57" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="A58" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B58" s="3" t="s">
         <v>222</v>
-      </c>
-      <c r="O57" s="6">
-        <v>47054</v>
-      </c>
-    </row>
-    <row r="58" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
-      <c r="A58" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="C58" s="2">
         <v>74331</v>
@@ -3907,13 +3867,13 @@
       <c r="E58" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F58" s="4" t="s">
-        <v>169</v>
+      <c r="F58" s="7" t="s">
+        <v>218</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H58" s="6">
+        <v>36</v>
+      </c>
+      <c r="H58" s="5">
         <v>45078</v>
       </c>
       <c r="I58" s="2">
@@ -3922,28 +3882,31 @@
       <c r="J58" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K58" s="6">
+      <c r="K58" s="5">
         <v>44774</v>
       </c>
-      <c r="L58" s="6">
+      <c r="L58" s="5">
         <v>35123</v>
       </c>
-      <c r="M58" s="6">
+      <c r="M58" s="5">
         <v>55579</v>
       </c>
       <c r="N58" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="O58" s="6">
+      <c r="O58" s="5">
         <v>47265</v>
       </c>
-    </row>
-    <row r="59" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P58" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A59" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>92</v>
+        <v>224</v>
       </c>
       <c r="C59" s="2">
         <v>75091</v>
@@ -3954,13 +3917,13 @@
       <c r="E59" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F59" s="4" t="s">
-        <v>169</v>
+      <c r="F59" s="7" t="s">
+        <v>218</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H59" s="6">
+        <v>36</v>
+      </c>
+      <c r="H59" s="5">
         <v>45108</v>
       </c>
       <c r="I59" s="2">
@@ -3969,28 +3932,31 @@
       <c r="J59" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K59" s="6">
+      <c r="K59" s="5">
         <v>44866</v>
       </c>
-      <c r="L59" s="6">
+      <c r="L59" s="5">
         <v>35615</v>
       </c>
-      <c r="M59" s="6">
+      <c r="M59" s="5">
         <v>56097</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="O59" s="6">
+        <v>225</v>
+      </c>
+      <c r="O59" s="5">
         <v>47324</v>
       </c>
-    </row>
-    <row r="60" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P59" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A60" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>93</v>
+        <v>226</v>
       </c>
       <c r="C60" s="2">
         <v>76820</v>
@@ -4001,13 +3967,13 @@
       <c r="E60" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F60" s="4" t="s">
-        <v>169</v>
+      <c r="F60" s="7" t="s">
+        <v>218</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H60" s="6">
+        <v>36</v>
+      </c>
+      <c r="H60" s="5">
         <v>45444</v>
       </c>
       <c r="I60" s="2">
@@ -4016,39 +3982,39 @@
       <c r="J60" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K60" s="6">
+      <c r="K60" s="5">
         <v>45289</v>
       </c>
-      <c r="L60" s="6">
+      <c r="L60" s="5">
         <v>36911</v>
       </c>
-      <c r="M60" s="6">
+      <c r="M60" s="5">
         <v>57377</v>
       </c>
     </row>
-    <row r="61" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A61" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>94</v>
+        <v>227</v>
       </c>
       <c r="C61" s="2">
         <v>69195</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>108</v>
+        <v>34</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>170</v>
+        <v>35</v>
+      </c>
+      <c r="F61" s="7" t="s">
+        <v>228</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H61" s="6">
+        <v>36</v>
+      </c>
+      <c r="H61" s="5">
         <v>45809</v>
       </c>
       <c r="I61" s="2">
@@ -4057,34 +4023,40 @@
       <c r="J61" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K61" s="6">
+      <c r="K61" s="5">
         <v>42562</v>
       </c>
-      <c r="L61" s="6">
+      <c r="L61" s="5">
         <v>33920</v>
       </c>
-      <c r="M61" s="6">
-        <v>54393</v>
+      <c r="M61" s="5">
+        <v>54424</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="O61" s="6">
+        <v>229</v>
+      </c>
+      <c r="O61" s="5">
         <v>46476</v>
       </c>
+      <c r="P61" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="Q61" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="R61" s="6">
+        <v>230</v>
+      </c>
+      <c r="R61" s="5">
         <v>47008</v>
       </c>
-    </row>
-    <row r="62" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="S61" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A62" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>95</v>
+        <v>231</v>
       </c>
       <c r="C62" s="2">
         <v>71068</v>
@@ -4095,13 +4067,13 @@
       <c r="E62" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F62" s="4" t="s">
-        <v>171</v>
+      <c r="F62" s="7" t="s">
+        <v>232</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H62" s="6">
+        <v>36</v>
+      </c>
+      <c r="H62" s="5">
         <v>45061</v>
       </c>
       <c r="I62" s="2">
@@ -4110,22 +4082,22 @@
       <c r="J62" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K62" s="6">
+      <c r="K62" s="5">
         <v>43009</v>
       </c>
-      <c r="L62" s="6">
+      <c r="L62" s="5">
         <v>34449</v>
       </c>
-      <c r="M62" s="6">
+      <c r="M62" s="5">
         <v>54909</v>
       </c>
     </row>
-    <row r="63" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A63" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>96</v>
+        <v>233</v>
       </c>
       <c r="C63" s="2">
         <v>73797</v>
@@ -4136,13 +4108,13 @@
       <c r="E63" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F63" s="4" t="s">
-        <v>172</v>
+      <c r="F63" s="7" t="s">
+        <v>234</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H63" s="6">
+        <v>36</v>
+      </c>
+      <c r="H63" s="5">
         <v>45884</v>
       </c>
       <c r="I63" s="2">
@@ -4151,22 +4123,22 @@
       <c r="J63" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K63" s="6">
+      <c r="K63" s="5">
         <v>43745</v>
       </c>
-      <c r="L63" s="6">
+      <c r="L63" s="5">
         <v>36046</v>
       </c>
-      <c r="M63" s="6">
+      <c r="M63" s="5">
         <v>56523</v>
       </c>
     </row>
-    <row r="64" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A64" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>97</v>
+        <v>235</v>
       </c>
       <c r="C64" s="2">
         <v>58908</v>
@@ -4177,13 +4149,13 @@
       <c r="E64" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F64" s="4" t="s">
-        <v>173</v>
+      <c r="F64" s="7" t="s">
+        <v>236</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H64" s="6">
+        <v>36</v>
+      </c>
+      <c r="H64" s="5">
         <v>44805</v>
       </c>
       <c r="I64" s="2">
@@ -4192,28 +4164,31 @@
       <c r="J64" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K64" s="6">
-        <v>40545</v>
-      </c>
-      <c r="L64" s="6">
+      <c r="K64" s="5">
+        <v>40575</v>
+      </c>
+      <c r="L64" s="5">
         <v>32859</v>
       </c>
-      <c r="M64" s="6">
+      <c r="M64" s="5">
         <v>53328</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="O64" s="6">
+        <v>237</v>
+      </c>
+      <c r="O64" s="5">
         <v>46916</v>
       </c>
-    </row>
-    <row r="65" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P64" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A65" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>98</v>
+        <v>238</v>
       </c>
       <c r="C65" s="2">
         <v>75240</v>
@@ -4222,15 +4197,15 @@
         <v>33</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F65" s="4" t="s">
-        <v>174</v>
+        <v>67</v>
+      </c>
+      <c r="F65" s="7" t="s">
+        <v>239</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H65" s="6">
+        <v>36</v>
+      </c>
+      <c r="H65" s="5">
         <v>44986</v>
       </c>
       <c r="I65" s="2">
@@ -4239,28 +4214,31 @@
       <c r="J65" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K65" s="6">
+      <c r="K65" s="5">
         <v>44896</v>
       </c>
-      <c r="L65" s="6">
+      <c r="L65" s="5">
         <v>35808</v>
       </c>
-      <c r="M65" s="6">
+      <c r="M65" s="5">
         <v>56281</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="O65" s="6">
+        <v>240</v>
+      </c>
+      <c r="O65" s="5">
         <v>47370</v>
       </c>
-    </row>
-    <row r="66" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P65" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A66" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>99</v>
+        <v>241</v>
       </c>
       <c r="C66" s="2">
         <v>76809</v>
@@ -4269,15 +4247,15 @@
         <v>33</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F66" s="4" t="s">
-        <v>174</v>
+        <v>67</v>
+      </c>
+      <c r="F66" s="7" t="s">
+        <v>239</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H66" s="6">
+        <v>36</v>
+      </c>
+      <c r="H66" s="5">
         <v>45444</v>
       </c>
       <c r="I66" s="2">
@@ -4286,22 +4264,22 @@
       <c r="J66" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K66" s="6">
+      <c r="K66" s="5">
         <v>45289</v>
       </c>
-      <c r="L66" s="6">
+      <c r="L66" s="5">
         <v>35572</v>
       </c>
-      <c r="M66" s="6">
+      <c r="M66" s="5">
         <v>56036</v>
       </c>
     </row>
-    <row r="67" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A67" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>100</v>
+        <v>242</v>
       </c>
       <c r="C67" s="2">
         <v>77295</v>
@@ -4310,15 +4288,15 @@
         <v>33</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F67" s="4" t="s">
-        <v>174</v>
+        <v>67</v>
+      </c>
+      <c r="F67" s="7" t="s">
+        <v>239</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H67" s="6">
+        <v>36</v>
+      </c>
+      <c r="H67" s="5">
         <v>45748</v>
       </c>
       <c r="I67" s="2">
@@ -4327,22 +4305,22 @@
       <c r="J67" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K67" s="6">
+      <c r="K67" s="5">
         <v>45642</v>
       </c>
-      <c r="L67" s="6">
+      <c r="L67" s="5">
         <v>36629</v>
       </c>
-      <c r="M67" s="6">
-        <v>46143</v>
-      </c>
-    </row>
-    <row r="68" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="M67" s="5">
+        <v>57101</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A68" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>101</v>
+        <v>243</v>
       </c>
       <c r="C68" s="2">
         <v>74984</v>
@@ -4351,16 +4329,16 @@
         <v>33</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="F68" s="4" t="s">
-        <v>175</v>
+        <v>46</v>
+      </c>
+      <c r="F68" s="7" t="s">
+        <v>244</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H68" s="6">
-        <v>45474</v>
+        <v>36</v>
+      </c>
+      <c r="H68" s="5">
+        <v>45078</v>
       </c>
       <c r="I68" s="2">
         <v>5</v>
@@ -4368,28 +4346,31 @@
       <c r="J68" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K68" s="6">
+      <c r="K68" s="5">
         <v>44866</v>
       </c>
-      <c r="L68" s="6">
+      <c r="L68" s="5">
         <v>36314</v>
       </c>
-      <c r="M68" s="6">
+      <c r="M68" s="5">
         <v>56796</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="O68" s="6">
+        <v>245</v>
+      </c>
+      <c r="O68" s="5">
         <v>46937</v>
       </c>
-    </row>
-    <row r="69" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P68" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A69" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>102</v>
+        <v>246</v>
       </c>
       <c r="C69" s="2">
         <v>75116</v>
@@ -4398,16 +4379,16 @@
         <v>33</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="F69" s="4" t="s">
-        <v>175</v>
+        <v>46</v>
+      </c>
+      <c r="F69" s="7" t="s">
+        <v>244</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H69" s="6">
-        <v>45474</v>
+        <v>36</v>
+      </c>
+      <c r="H69" s="5">
+        <v>45078</v>
       </c>
       <c r="I69" s="2">
         <v>5</v>
@@ -4415,22 +4396,22 @@
       <c r="J69" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K69" s="6">
+      <c r="K69" s="5">
         <v>44866</v>
       </c>
-      <c r="L69" s="6">
+      <c r="L69" s="5">
         <v>35358</v>
       </c>
-      <c r="M69" s="6">
+      <c r="M69" s="5">
         <v>55824</v>
       </c>
     </row>
-    <row r="70" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A70" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>103</v>
+        <v>247</v>
       </c>
       <c r="C70" s="2">
         <v>75080</v>
@@ -4439,15 +4420,15 @@
         <v>33</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="F70" s="4" t="s">
-        <v>175</v>
+        <v>46</v>
+      </c>
+      <c r="F70" s="7" t="s">
+        <v>244</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H70" s="6">
+        <v>36</v>
+      </c>
+      <c r="H70" s="5">
         <v>45108</v>
       </c>
       <c r="I70" s="2">
@@ -4456,46 +4437,49 @@
       <c r="J70" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K70" s="6">
+      <c r="K70" s="5">
         <v>44866</v>
       </c>
-      <c r="L70" s="6">
+      <c r="L70" s="5">
         <v>35318</v>
       </c>
-      <c r="M70" s="6">
+      <c r="M70" s="5">
         <v>55793</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="O70" s="6">
+        <v>248</v>
+      </c>
+      <c r="O70" s="5">
         <v>47265</v>
       </c>
-    </row>
-    <row r="71" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P70" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A71" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>104</v>
+        <v>249</v>
       </c>
       <c r="C71" s="2">
         <v>41117</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>108</v>
+        <v>34</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F71" s="4" t="s">
-        <v>176</v>
+        <v>35</v>
+      </c>
+      <c r="F71" s="7" t="s">
+        <v>250</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H71" s="6">
-        <v>46060</v>
+        <v>36</v>
+      </c>
+      <c r="H71" s="5">
+        <v>45792</v>
       </c>
       <c r="I71" s="2">
         <v>11</v>
@@ -4503,34 +4487,31 @@
       <c r="J71" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K71" s="6">
+      <c r="K71" s="5">
         <v>34304</v>
       </c>
-      <c r="L71" s="6">
+      <c r="L71" s="5">
         <v>26307</v>
       </c>
-      <c r="M71" s="6">
+      <c r="M71" s="5">
         <v>46784</v>
       </c>
-      <c r="N71" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="O71" s="6">
+      <c r="Q71" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="R71" s="5">
         <v>47005</v>
       </c>
-      <c r="Q71" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="R71" s="6">
-        <v>47005</v>
-      </c>
-    </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="S71" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A72" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>105</v>
+        <v>252</v>
       </c>
       <c r="C72" s="2">
         <v>70626</v>
@@ -4541,13 +4522,13 @@
       <c r="E72" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F72" s="4" t="s">
-        <v>177</v>
+      <c r="F72" s="7" t="s">
+        <v>253</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H72" s="6">
+        <v>36</v>
+      </c>
+      <c r="H72" s="5">
         <v>45474</v>
       </c>
       <c r="I72" s="2">
@@ -4556,28 +4537,31 @@
       <c r="J72" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K72" s="6">
+      <c r="K72" s="5">
         <v>42705</v>
       </c>
-      <c r="L72" s="6">
+      <c r="L72" s="5">
         <v>33919</v>
       </c>
-      <c r="M72" s="6">
+      <c r="M72" s="5">
         <v>54393</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="O72" s="6">
+        <v>254</v>
+      </c>
+      <c r="O72" s="5">
         <v>46595</v>
       </c>
-    </row>
-    <row r="73" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P72" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A73" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>106</v>
+        <v>255</v>
       </c>
       <c r="C73" s="2">
         <v>76846</v>
@@ -4588,13 +4572,13 @@
       <c r="E73" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F73" s="4" t="s">
-        <v>178</v>
+      <c r="F73" s="7" t="s">
+        <v>256</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H73" s="6">
+        <v>36</v>
+      </c>
+      <c r="H73" s="5">
         <v>45444</v>
       </c>
       <c r="I73" s="2">
@@ -4603,22 +4587,22 @@
       <c r="J73" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K73" s="6">
+      <c r="K73" s="5">
         <v>45289</v>
       </c>
-      <c r="L73" s="6">
+      <c r="L73" s="5">
         <v>36894</v>
       </c>
-      <c r="M73" s="6">
+      <c r="M73" s="5">
         <v>57377</v>
       </c>
     </row>
-    <row r="74" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A74" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>107</v>
+        <v>257</v>
       </c>
       <c r="C74" s="2">
         <v>74614</v>
@@ -4629,13 +4613,13 @@
       <c r="E74" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F74" s="4" t="s">
-        <v>178</v>
+      <c r="F74" s="7" t="s">
+        <v>256</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H74" s="6">
+        <v>36</v>
+      </c>
+      <c r="H74" s="5">
         <v>45078</v>
       </c>
       <c r="I74" s="2">
@@ -4644,45 +4628,193 @@
       <c r="J74" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K74" s="6">
+      <c r="K74" s="5">
         <v>44866</v>
       </c>
-      <c r="L74" s="6">
+      <c r="L74" s="5">
         <v>34871</v>
       </c>
-      <c r="M74" s="6">
+      <c r="M74" s="5">
         <v>55335</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="O74" s="6">
+        <v>258</v>
+      </c>
+      <c r="O74" s="5">
         <v>47324</v>
       </c>
-    </row>
+      <c r="P74" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.45"/>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.45"/>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.45"/>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.45"/>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.45"/>
+    <row r="80" spans="1:19" x14ac:dyDescent="0.45"/>
+    <row r="81" x14ac:dyDescent="0.45"/>
+    <row r="82" x14ac:dyDescent="0.45"/>
+    <row r="83" x14ac:dyDescent="0.45"/>
+    <row r="84" x14ac:dyDescent="0.45"/>
+    <row r="85" x14ac:dyDescent="0.45"/>
+    <row r="86" x14ac:dyDescent="0.45"/>
+    <row r="87" x14ac:dyDescent="0.45"/>
+    <row r="88" x14ac:dyDescent="0.45"/>
+    <row r="89" x14ac:dyDescent="0.45"/>
+    <row r="90" x14ac:dyDescent="0.45"/>
+    <row r="91" x14ac:dyDescent="0.45"/>
+    <row r="92" x14ac:dyDescent="0.45"/>
+    <row r="93" x14ac:dyDescent="0.45"/>
+    <row r="94" x14ac:dyDescent="0.45"/>
+    <row r="95" x14ac:dyDescent="0.45"/>
+    <row r="96" x14ac:dyDescent="0.45"/>
+    <row r="97" x14ac:dyDescent="0.45"/>
+    <row r="98" x14ac:dyDescent="0.45"/>
+    <row r="99" x14ac:dyDescent="0.45"/>
+    <row r="100" x14ac:dyDescent="0.45"/>
+    <row r="101" x14ac:dyDescent="0.45"/>
+    <row r="102" x14ac:dyDescent="0.45"/>
+    <row r="103" x14ac:dyDescent="0.45"/>
+    <row r="104" x14ac:dyDescent="0.45"/>
+    <row r="105" x14ac:dyDescent="0.45"/>
+    <row r="106" x14ac:dyDescent="0.45"/>
+    <row r="107" x14ac:dyDescent="0.45"/>
+    <row r="108" x14ac:dyDescent="0.45"/>
+    <row r="109" x14ac:dyDescent="0.45"/>
+    <row r="110" x14ac:dyDescent="0.45"/>
+    <row r="111" x14ac:dyDescent="0.45"/>
+    <row r="112" x14ac:dyDescent="0.45"/>
+    <row r="113" x14ac:dyDescent="0.45"/>
+    <row r="114" x14ac:dyDescent="0.45"/>
+    <row r="115" x14ac:dyDescent="0.45"/>
+    <row r="116" x14ac:dyDescent="0.45"/>
+    <row r="117" x14ac:dyDescent="0.45"/>
+    <row r="118" x14ac:dyDescent="0.45"/>
+    <row r="119" x14ac:dyDescent="0.45"/>
+    <row r="120" x14ac:dyDescent="0.45"/>
+    <row r="121" x14ac:dyDescent="0.45"/>
+    <row r="122" x14ac:dyDescent="0.45"/>
+    <row r="123" x14ac:dyDescent="0.45"/>
+    <row r="124" x14ac:dyDescent="0.45"/>
+    <row r="125" x14ac:dyDescent="0.45"/>
+    <row r="126" x14ac:dyDescent="0.45"/>
+    <row r="127" x14ac:dyDescent="0.45"/>
+    <row r="128" x14ac:dyDescent="0.45"/>
+    <row r="129" x14ac:dyDescent="0.45"/>
+    <row r="130" x14ac:dyDescent="0.45"/>
+    <row r="131" x14ac:dyDescent="0.45"/>
+    <row r="132" x14ac:dyDescent="0.45"/>
+    <row r="133" x14ac:dyDescent="0.45"/>
+    <row r="134" x14ac:dyDescent="0.45"/>
+    <row r="135" x14ac:dyDescent="0.45"/>
+    <row r="136" x14ac:dyDescent="0.45"/>
+    <row r="137" x14ac:dyDescent="0.45"/>
+    <row r="138" x14ac:dyDescent="0.45"/>
+    <row r="139" x14ac:dyDescent="0.45"/>
+    <row r="140" x14ac:dyDescent="0.45"/>
+    <row r="141" x14ac:dyDescent="0.45"/>
+    <row r="142" x14ac:dyDescent="0.45"/>
+    <row r="143" x14ac:dyDescent="0.45"/>
+    <row r="144" x14ac:dyDescent="0.45"/>
+    <row r="145" x14ac:dyDescent="0.45"/>
+    <row r="146" x14ac:dyDescent="0.45"/>
+    <row r="147" x14ac:dyDescent="0.45"/>
+    <row r="148" x14ac:dyDescent="0.45"/>
+    <row r="149" x14ac:dyDescent="0.45"/>
+    <row r="150" x14ac:dyDescent="0.45"/>
+    <row r="151" x14ac:dyDescent="0.45"/>
+    <row r="152" x14ac:dyDescent="0.45"/>
+    <row r="153" x14ac:dyDescent="0.45"/>
+    <row r="154" x14ac:dyDescent="0.45"/>
+    <row r="155" x14ac:dyDescent="0.45"/>
+    <row r="156" x14ac:dyDescent="0.45"/>
+    <row r="157" x14ac:dyDescent="0.45"/>
+    <row r="158" x14ac:dyDescent="0.45"/>
+    <row r="159" x14ac:dyDescent="0.45"/>
+    <row r="160" x14ac:dyDescent="0.45"/>
+    <row r="161" x14ac:dyDescent="0.45"/>
+    <row r="162" x14ac:dyDescent="0.45"/>
+    <row r="163" x14ac:dyDescent="0.45"/>
+    <row r="164" x14ac:dyDescent="0.45"/>
+    <row r="165" x14ac:dyDescent="0.45"/>
+    <row r="166" x14ac:dyDescent="0.45"/>
+    <row r="167" x14ac:dyDescent="0.45"/>
+    <row r="168" x14ac:dyDescent="0.45"/>
+    <row r="169" x14ac:dyDescent="0.45"/>
+    <row r="170" x14ac:dyDescent="0.45"/>
+    <row r="171" x14ac:dyDescent="0.45"/>
+    <row r="172" x14ac:dyDescent="0.45"/>
+    <row r="173" x14ac:dyDescent="0.45"/>
+    <row r="174" x14ac:dyDescent="0.45"/>
+    <row r="175" x14ac:dyDescent="0.45"/>
+    <row r="176" x14ac:dyDescent="0.45"/>
+    <row r="177" x14ac:dyDescent="0.45"/>
+    <row r="178" x14ac:dyDescent="0.45"/>
+    <row r="179" x14ac:dyDescent="0.45"/>
+    <row r="180" x14ac:dyDescent="0.45"/>
+    <row r="181" x14ac:dyDescent="0.45"/>
+    <row r="182" x14ac:dyDescent="0.45"/>
+    <row r="183" x14ac:dyDescent="0.45"/>
+    <row r="184" x14ac:dyDescent="0.45"/>
+    <row r="185" x14ac:dyDescent="0.45"/>
+    <row r="186" x14ac:dyDescent="0.45"/>
+    <row r="187" x14ac:dyDescent="0.45"/>
+    <row r="188" x14ac:dyDescent="0.45"/>
+    <row r="189" x14ac:dyDescent="0.45"/>
+    <row r="190" x14ac:dyDescent="0.45"/>
+    <row r="191" x14ac:dyDescent="0.45"/>
+    <row r="192" x14ac:dyDescent="0.45"/>
+    <row r="193" x14ac:dyDescent="0.45"/>
+    <row r="194" x14ac:dyDescent="0.45"/>
+    <row r="195" x14ac:dyDescent="0.45"/>
+    <row r="196" x14ac:dyDescent="0.45"/>
+    <row r="197" x14ac:dyDescent="0.45"/>
+    <row r="198" x14ac:dyDescent="0.45"/>
+    <row r="199" x14ac:dyDescent="0.45"/>
+    <row r="200" x14ac:dyDescent="0.45"/>
   </sheetData>
+  <autoFilter ref="A1:T199" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>LIST_DATA!$A$1:$A$9</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D1000</xm:sqref>
+          <xm:sqref>D2:D986</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
             <xm:f>LIST_DATA!$B$1:$B$6</xm:f>
           </x14:formula1>
-          <xm:sqref>J2:J1000</xm:sqref>
+          <xm:sqref>J2:J986</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000002000000}">
           <x14:formula1>
             <xm:f>LIST_DATA!$C$1:$C$15</xm:f>
           </x14:formula1>
-          <xm:sqref>I2:I1000</xm:sqref>
+          <xm:sqref>I2:I986</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{354EFE19-C43E-4A2D-83B1-FD15C013476E}">
+          <x14:formula1>
+            <xm:f>LIST_DATA!$D:$D</xm:f>
+          </x14:formula1>
+          <xm:sqref>G2:G200</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9DE71029-D453-4F4E-B557-CC5A72AEA9EB}">
+          <x14:formula1>
+            <xm:f>LIST_DATA!$E:$E</xm:f>
+          </x14:formula1>
+          <xm:sqref>P2:P200 S2:S200</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{262E53F9-7911-451D-88C9-1E420930ED84}">
+          <x14:formula1>
+            <xm:f>LIST_DATA!$F:$F</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E200</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -4692,130 +4824,297 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="13.59765625" customWidth="1"/>
+    <col min="1" max="1" width="16.73046875" style="8" customWidth="1"/>
+    <col min="2" max="3" width="9.06640625" style="8"/>
+    <col min="4" max="4" width="14.46484375" style="8" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="6" max="6" width="49.53125" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C1">
+      <c r="C1" s="8">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
+      <c r="D1" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A2" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="8">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
+      <c r="D2" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="8">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
+      <c r="D3" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A4" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="8">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="D4" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A5" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="8">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
+      <c r="D5" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A6" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="8">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
+      <c r="D6" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A7" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="8">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
+      <c r="D7" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="8">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
+      <c r="D8" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A9" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="8">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C10">
+      <c r="D9" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C10" s="8">
         <v>13</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C11">
+      <c r="D10" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C11" s="8">
         <v>14</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C12">
+      <c r="D11" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C12" s="8">
         <v>15</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C13">
+      <c r="D12" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C13" s="8">
         <v>16</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C14">
+      <c r="D13" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C14" s="8">
         <v>17</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C15">
+      <c r="D14" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C15" s="8">
         <v>18</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="D16" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="D17" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F18" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F19" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F20" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F21" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F22" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F23" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F24" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F25" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F26" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
